--- a/tests/testthat/excel/mapping_neu.xlsx
+++ b/tests/testthat/excel/mapping_neu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9FA419-E7F0-437C-9092-82E1700B70F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328A15E7-A9F5-4382-8626-2F98CBDA4309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15525" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15525" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -1729,13 +1729,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>800100</xdr:colOff>
+          <xdr:colOff>352425</xdr:colOff>
           <xdr:row>0</xdr:row>
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>2324100</xdr:colOff>
+          <xdr:colOff>1876425</xdr:colOff>
           <xdr:row>0</xdr:row>
           <xdr:rowOff>228600</xdr:rowOff>
         </xdr:to>
@@ -14569,10 +14569,7 @@
       <c r="M3" s="25"/>
       <c r="N3" s="25"/>
       <c r="O3" s="25"/>
-      <c r="P3" s="31" t="str">
-        <f t="shared" ref="P3:P18" si="0">IF(B3&lt;&gt;"",A3&amp;"}"&amp;B3,"")</f>
-        <v/>
-      </c>
+      <c r="P3" s="31"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
       <c r="S3" s="25"/>
@@ -14611,10 +14608,7 @@
       <c r="M4" s="25"/>
       <c r="N4" s="25"/>
       <c r="O4" s="25"/>
-      <c r="P4" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="P4" s="31"/>
       <c r="Q4" s="25"/>
       <c r="R4" s="25"/>
       <c r="S4" s="25"/>
@@ -14663,10 +14657,7 @@
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
       <c r="O5" s="25"/>
-      <c r="P5" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>}Region</v>
-      </c>
+      <c r="P5" s="31"/>
       <c r="Q5" s="31"/>
       <c r="R5" s="25"/>
       <c r="S5" s="25"/>
@@ -14720,10 +14711,7 @@
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
       <c r="O6" s="25"/>
-      <c r="P6" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q1}1. Wie viele Mitarbeiter beschäftigt Ihr Unternehmen?</v>
-      </c>
+      <c r="P6" s="31"/>
       <c r="Q6" s="31"/>
       <c r="R6" s="31"/>
       <c r="S6" s="31"/>
@@ -14752,7 +14740,7 @@
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="str">
-        <f t="shared" ref="A7:A18" si="1">"Q"&amp;LEFT(B7,FIND(".",B7)-1)</f>
+        <f t="shared" ref="A7:A18" si="0">"Q"&amp;LEFT(B7,FIND(".",B7)-1)</f>
         <v>Q2</v>
       </c>
       <c r="B7" s="30" t="s">
@@ -14777,10 +14765,7 @@
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q2}2. Welche Art von Studien führen Sie mit dem Tabellenbandtool durch?' 'DC#SELVALLAB</v>
-      </c>
+      <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
       <c r="R7" s="31"/>
       <c r="S7" s="31" t="s">
@@ -14813,7 +14798,7 @@
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q3</v>
       </c>
       <c r="B8" s="30" t="s">
@@ -14840,10 +14825,7 @@
         <v>259</v>
       </c>
       <c r="O8" s="25"/>
-      <c r="P8" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q3}3. Wie verteilten sich die Studien prozentual auf die einzelnen Arten?</v>
-      </c>
+      <c r="P8" s="31"/>
       <c r="Q8" s="31"/>
       <c r="R8" s="31"/>
       <c r="S8" s="31"/>
@@ -14872,7 +14854,7 @@
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q4</v>
       </c>
       <c r="B9" s="30" t="s">
@@ -14903,10 +14885,7 @@
         <v>263</v>
       </c>
       <c r="O9" s="25"/>
-      <c r="P9" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">Q4}4. Wie häufig haben Sie einen Tabellenband in den letzten 12 Monaten erstellen lassen? </v>
-      </c>
+      <c r="P9" s="31"/>
       <c r="Q9" s="31"/>
       <c r="R9" s="31"/>
       <c r="S9" s="31"/>
@@ -14935,7 +14914,7 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q5</v>
       </c>
       <c r="B10" s="30" t="s">
@@ -14960,10 +14939,7 @@
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q5}5. Was lief besonders gut in den Projekten?</v>
-      </c>
+      <c r="P10" s="31"/>
       <c r="Q10" s="31" t="s">
         <v>294</v>
       </c>
@@ -14996,7 +14972,7 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q5</v>
       </c>
       <c r="B11" s="30" t="s">
@@ -15027,10 +15003,7 @@
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q5}5. Was lief besonders gut in den Projekten?</v>
-      </c>
+      <c r="P11" s="31"/>
       <c r="Q11" s="31" t="s">
         <v>295</v>
       </c>
@@ -15061,7 +15034,7 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q5</v>
       </c>
       <c r="B12" s="30" t="s">
@@ -15092,10 +15065,7 @@
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q5}5. Was lief besonders gut in den Projekten?</v>
-      </c>
+      <c r="P12" s="31"/>
       <c r="Q12" s="31"/>
       <c r="R12" s="31"/>
       <c r="S12" s="31"/>
@@ -15146,10 +15116,7 @@
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>}Abgefragte Studienarten</v>
-      </c>
+      <c r="P13" s="31"/>
       <c r="Q13" s="31" t="s">
         <v>296</v>
       </c>
@@ -15182,7 +15149,7 @@
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q6</v>
       </c>
       <c r="B14" s="30" t="s">
@@ -15213,10 +15180,7 @@
         <v>259</v>
       </c>
       <c r="O14" s="25"/>
-      <c r="P14" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q6}6. Ich nenne Ihnen gleich einige generelle Merkmale, die bei quantitativen Forschungsprojekten eine Rolle spielen. Bitte stufen Sie die Wichtigkeit ein.</v>
-      </c>
+      <c r="P14" s="31"/>
       <c r="Q14" s="31"/>
       <c r="R14" s="31"/>
       <c r="S14" s="31"/>
@@ -15249,7 +15213,7 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q7</v>
       </c>
       <c r="B15" s="30" t="s">
@@ -15280,10 +15244,7 @@
         <v>259</v>
       </c>
       <c r="O15" s="25"/>
-      <c r="P15" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q7}7. Für die abgefragten Studienarten: Wie zufrieden sind Sie mit dem Tabellenbandtool bezüglich der eben abgefragten Merkmale?' 'DC#SELVALLAB</v>
-      </c>
+      <c r="P15" s="31"/>
       <c r="Q15" s="31"/>
       <c r="R15" s="31"/>
       <c r="S15" s="31" t="s">
@@ -15318,7 +15279,7 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q8</v>
       </c>
       <c r="B16" s="30" t="s">
@@ -15349,10 +15310,7 @@
         <v>259</v>
       </c>
       <c r="O16" s="25"/>
-      <c r="P16" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q8}8. Wie zufrieden sind Sie mit dem Tabellenbandtool insgesamt?' 'DC#SELVALLAB</v>
-      </c>
+      <c r="P16" s="31"/>
       <c r="Q16" s="31"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31" t="s">
@@ -15385,7 +15343,7 @@
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q9</v>
       </c>
       <c r="B17" s="30" t="s">
@@ -15414,10 +15372,7 @@
       <c r="M17" s="31"/>
       <c r="N17" s="31"/>
       <c r="O17" s="25"/>
-      <c r="P17" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q9}9. Würden Sie das Tabellenbandtool weiterempfehlen?' 'DC#SELVALLAB</v>
-      </c>
+      <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31" t="s">
@@ -15450,7 +15405,7 @@
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Q10</v>
       </c>
       <c r="B18" s="30" t="s">
@@ -15479,10 +15434,7 @@
         <v>263</v>
       </c>
       <c r="O18" s="25"/>
-      <c r="P18" s="31" t="str">
-        <f t="shared" si="0"/>
-        <v>Q10}10. Dürfte ich Sie noch nach Ihrem Alter fragen?</v>
-      </c>
+      <c r="P18" s="31"/>
       <c r="Q18" s="31"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
@@ -41287,13 +41239,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>800100</xdr:colOff>
+                    <xdr:colOff>352425</xdr:colOff>
                     <xdr:row>0</xdr:row>
                     <xdr:rowOff>47625</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>2324100</xdr:colOff>
+                    <xdr:colOff>1876425</xdr:colOff>
                     <xdr:row>0</xdr:row>
                     <xdr:rowOff>228600</xdr:rowOff>
                   </to>

--- a/tests/testthat/excel/mapping_neu.xlsx
+++ b/tests/testthat/excel/mapping_neu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Projects\UW git\crosstabser\tests\testthat\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328A15E7-A9F5-4382-8626-2F98CBDA4309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF55821A-93F3-4654-BCAA-88FA97E5814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15525" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,28 +19,26 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="V_Datum">Config!$B$18</definedName>
-    <definedName name="V_ErrCountLog10">[1]Log10!$D$1</definedName>
-    <definedName name="V_ErrCountLog20">[1]Log20!$D$1</definedName>
-    <definedName name="V_ErrCountLog40">[1]Log40!$D$1</definedName>
-    <definedName name="V_ErrCountLog40Warn">[1]Log40Warn!$D$1</definedName>
+    <definedName name="V_ErrCountLog10">#REF!</definedName>
+    <definedName name="V_ErrCountLog20">#REF!</definedName>
+    <definedName name="V_ErrCountLog40">#REF!</definedName>
+    <definedName name="V_ErrCountLog40Warn">#REF!</definedName>
     <definedName name="V_Language">Config!$B$15</definedName>
-    <definedName name="V_Lexikon">[2]Lexikon!$A$2:$H$192</definedName>
+    <definedName name="V_Lexikon">#REF!</definedName>
     <definedName name="V_Namenszusatz">Config!$B$17</definedName>
-    <definedName name="V_Projektleiter">Config!$B$38</definedName>
-    <definedName name="V_ProjektleiterCol">Config!$C$38</definedName>
+    <definedName name="V_Projektleiter">Config!$B$39</definedName>
+    <definedName name="V_ProjektleiterCol">Config!$C$39</definedName>
     <definedName name="V_Projektname">Config!$B$21</definedName>
     <definedName name="V_Projektverzeichnis">Config!$B$20</definedName>
     <definedName name="V_Scenario">Config!$B$16</definedName>
-    <definedName name="V_ScenDetail">[1]Macro!$E$3:$BB$43</definedName>
+    <definedName name="V_ScenDetail">#REF!</definedName>
     <definedName name="V_ScenName">Config!$C$16</definedName>
-    <definedName name="V_TemplatePath">Config!$B$26</definedName>
-    <definedName name="V_Variablen">[3]Variables!$V:$X</definedName>
+    <definedName name="V_TemplatePath">Config!$B$27</definedName>
+    <definedName name="V_Variablen">#REF!</definedName>
+    <definedName name="V_XMLName">Config!$B$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,6 +61,29 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Wolf Wilke</author>
+  </authors>
+  <commentList>
+    <comment ref="A23" authorId="0" shapeId="0" xr:uid="{55BAE0B3-D31C-4026-AEC7-838494A478E9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Name of XML file with table date, to be appended by '&lt;QuestNo&gt;.xml'</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>wolf</author>
@@ -163,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="323">
   <si>
     <t>Make script</t>
   </si>
@@ -1127,6 +1148,12 @@
   <si>
     <t>ColVar</t>
   </si>
+  <si>
+    <t>XML name</t>
+  </si>
+  <si>
+    <t>dev\xml\XML_test_Draft_</t>
+  </si>
 </sst>
 </file>
 
@@ -1211,7 +1238,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1302,6 +1329,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1316,7 +1349,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1357,19 +1390,30 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1379,16 +1423,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1540,7 +1574,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="40" dropStyle="combo" dx="16" fmlaLink="[3]Config!$K$16" fmlaRange="[4]!V_TemplateFill" noThreeD="1" sel="0" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="40" dropStyle="combo" dx="16" fmlaRange="[1]!V_TemplateFill" noThreeD="1" sel="0" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1637,12 +1671,12 @@
       <xdr:rowOff>31745</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="203246" cy="203246"/>
-    <xdr:pic macro="[4]!SF40_KlickenSieAuf">
+    <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="TabellenErzeugen">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{276AF167-0659-44C4-B363-6A33BBE3309C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1687,12 +1721,12 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>234996</xdr:rowOff>
     </xdr:to>
-    <xdr:pic macro="[4]!SF40_SelectedKlickenSieAuf">
+    <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="AusgewaehlteTabellenErzeugen">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{233F5AF7-C84D-4606-A910-ED223F629818}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1747,7 +1781,7 @@
                   <a14:compatExt spid="_x0000_s2051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A0C1BDF-3CC8-4CD5-8030-C77B7562FC4A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1788,7784 +1822,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Config"/>
-      <sheetName val="Data"/>
-      <sheetName val="Variables"/>
-      <sheetName val="Label"/>
-      <sheetName val="Verbatims"/>
-      <sheetName val="VerbCodeR"/>
-      <sheetName val="VerbCode"/>
-      <sheetName val="Free1"/>
-      <sheetName val="Free2"/>
-      <sheetName val="Macro"/>
-      <sheetName val="Questions"/>
-      <sheetName val="RLog"/>
-      <sheetName val="Log10"/>
-      <sheetName val="Log20"/>
-      <sheetName val="Log40"/>
-      <sheetName val="Log40Warn"/>
-      <sheetName val="Tabelle1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Hinweis"/>
-      <sheetName val="Vorlage Verbatims"/>
-      <sheetName val="Vorgaben Questions"/>
-      <sheetName val="Projektleiter"/>
-      <sheetName val="Lexikon"/>
-      <sheetName val="Limesurvey"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Config"/>
-      <sheetName val="Data"/>
-      <sheetName val="Variables"/>
-      <sheetName val="Label"/>
-      <sheetName val="Verbatims"/>
-      <sheetName val="VerbCode"/>
-      <sheetName val="Free1"/>
-      <sheetName val="Free2"/>
-      <sheetName val="Macro"/>
-      <sheetName val="Questions"/>
-      <sheetName val="Log10"/>
-      <sheetName val="Log20"/>
-      <sheetName val="Log40"/>
-      <sheetName val="Tabelle1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="3">
-          <cell r="V3" t="str">
-            <v>DC_</v>
-          </cell>
-          <cell r="W3" t="str">
-            <v>DC_</v>
-          </cell>
-          <cell r="X3" t="str">
-            <v xml:space="preserve">DC_ID </v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="V4" t="str">
-            <v>id</v>
-          </cell>
-          <cell r="W4" t="str">
-            <v>id</v>
-          </cell>
-          <cell r="X4" t="str">
-            <v xml:space="preserve">id </v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="V5" t="str">
-            <v>scr</v>
-          </cell>
-          <cell r="W5" t="str">
-            <v>scr</v>
-          </cell>
-          <cell r="X5" t="str">
-            <v xml:space="preserve">screenout </v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="V6" t="str">
-            <v>dat</v>
-          </cell>
-          <cell r="W6" t="str">
-            <v>dat</v>
-          </cell>
-          <cell r="X6" t="str">
-            <v xml:space="preserve">datum </v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="V7" t="str">
-            <v>q1</v>
-          </cell>
-          <cell r="W7" t="str">
-            <v>q1</v>
-          </cell>
-          <cell r="X7" t="str">
-            <v xml:space="preserve">q1 </v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="V8" t="str">
-            <v/>
-          </cell>
-          <cell r="W8" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X8" t="str">
-            <v/>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="V9" t="str">
-            <v/>
-          </cell>
-          <cell r="W9" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X9" t="str">
-            <v xml:space="preserve">q2_01 </v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="V10" t="str">
-            <v/>
-          </cell>
-          <cell r="W10" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X10" t="str">
-            <v xml:space="preserve">q2_01 q2_02 </v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="V11" t="str">
-            <v/>
-          </cell>
-          <cell r="W11" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X11" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 </v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="V12" t="str">
-            <v/>
-          </cell>
-          <cell r="W12" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X12" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 q2_04 </v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="V13" t="str">
-            <v/>
-          </cell>
-          <cell r="W13" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X13" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 q2_04 q2_05 </v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="V14" t="str">
-            <v/>
-          </cell>
-          <cell r="W14" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X14" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 q2_04 q2_05 q2_06 </v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="V15" t="str">
-            <v/>
-          </cell>
-          <cell r="W15" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X15" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 q2_04 q2_05 q2_06 q2_07 </v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="V16" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="W16" t="str">
-            <v>q2</v>
-          </cell>
-          <cell r="X16" t="str">
-            <v xml:space="preserve">q2_01 q2_02 q2_03 q2_04 q2_05 q2_06 q2_07 </v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="V17" t="str">
-            <v/>
-          </cell>
-          <cell r="W17" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X17" t="str">
-            <v xml:space="preserve">q3a </v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="V18" t="str">
-            <v/>
-          </cell>
-          <cell r="W18" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X18" t="str">
-            <v xml:space="preserve">q3a q3b </v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="V19" t="str">
-            <v/>
-          </cell>
-          <cell r="W19" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X19" t="str">
-            <v xml:space="preserve">q3a q3b q3c </v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="V20" t="str">
-            <v/>
-          </cell>
-          <cell r="W20" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X20" t="str">
-            <v xml:space="preserve">q3a q3b q3c q3d </v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="V21" t="str">
-            <v/>
-          </cell>
-          <cell r="W21" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X21" t="str">
-            <v xml:space="preserve">q3a q3b q3c q3d q3e </v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="V22" t="str">
-            <v/>
-          </cell>
-          <cell r="W22" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X22" t="str">
-            <v xml:space="preserve">q3a q3b q3c q3d q3e q3f </v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="V23" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="W23" t="str">
-            <v>q3</v>
-          </cell>
-          <cell r="X23" t="str">
-            <v xml:space="preserve">q3a q3b q3c q3d q3e q3f q3g </v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="V24" t="str">
-            <v>q4</v>
-          </cell>
-          <cell r="W24" t="str">
-            <v>q4</v>
-          </cell>
-          <cell r="X24" t="str">
-            <v xml:space="preserve">q4 </v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="V25" t="str">
-            <v/>
-          </cell>
-          <cell r="W25" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X25" t="str">
-            <v xml:space="preserve">q6a </v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="V26" t="str">
-            <v/>
-          </cell>
-          <cell r="W26" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X26" t="str">
-            <v xml:space="preserve">q6a q6b </v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="V27" t="str">
-            <v/>
-          </cell>
-          <cell r="W27" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X27" t="str">
-            <v xml:space="preserve">q6a q6b q6c </v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="V28" t="str">
-            <v/>
-          </cell>
-          <cell r="W28" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X28" t="str">
-            <v xml:space="preserve">q6a q6b q6c q6d </v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="V29" t="str">
-            <v/>
-          </cell>
-          <cell r="W29" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X29" t="str">
-            <v xml:space="preserve">q6a q6b q6c q6d q6e </v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="V30" t="str">
-            <v/>
-          </cell>
-          <cell r="W30" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X30" t="str">
-            <v xml:space="preserve">q6a q6b q6c q6d q6e q6f </v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="V31" t="str">
-            <v/>
-          </cell>
-          <cell r="W31" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X31" t="str">
-            <v xml:space="preserve">q6a q6b q6c q6d q6e q6f q6g </v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="V32" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="W32" t="str">
-            <v>q6</v>
-          </cell>
-          <cell r="X32" t="str">
-            <v xml:space="preserve">q6a q6b q6c q6d q6e q6f q6g q6h </v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="V33" t="str">
-            <v>se</v>
-          </cell>
-          <cell r="W33" t="str">
-            <v>se</v>
-          </cell>
-          <cell r="X33" t="str">
-            <v xml:space="preserve">sel1 </v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="V34" t="str">
-            <v/>
-          </cell>
-          <cell r="W34" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X34" t="str">
-            <v xml:space="preserve">q7a1 </v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="V35" t="str">
-            <v/>
-          </cell>
-          <cell r="W35" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X35" t="str">
-            <v xml:space="preserve">q7a1 q7a2 </v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="V36" t="str">
-            <v/>
-          </cell>
-          <cell r="W36" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X36" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 </v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="V37" t="str">
-            <v/>
-          </cell>
-          <cell r="W37" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X37" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 </v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="V38" t="str">
-            <v/>
-          </cell>
-          <cell r="W38" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X38" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 </v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="V39" t="str">
-            <v/>
-          </cell>
-          <cell r="W39" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X39" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 </v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="V40" t="str">
-            <v/>
-          </cell>
-          <cell r="W40" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X40" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 </v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="V41" t="str">
-            <v/>
-          </cell>
-          <cell r="W41" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X41" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 </v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="V42" t="str">
-            <v/>
-          </cell>
-          <cell r="W42" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X42" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 </v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="V43" t="str">
-            <v/>
-          </cell>
-          <cell r="W43" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X43" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 </v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="V44" t="str">
-            <v/>
-          </cell>
-          <cell r="W44" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X44" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 </v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="V45" t="str">
-            <v/>
-          </cell>
-          <cell r="W45" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X45" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 q7h2 </v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="V46" t="str">
-            <v/>
-          </cell>
-          <cell r="W46" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X46" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 q7h2 q7f1 </v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="V47" t="str">
-            <v/>
-          </cell>
-          <cell r="W47" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X47" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 q7h2 q7f1 q7f2 </v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="V48" t="str">
-            <v/>
-          </cell>
-          <cell r="W48" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X48" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 q7h2 q7f1 q7f2 q7g1 </v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="V49" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="W49" t="str">
-            <v>q7</v>
-          </cell>
-          <cell r="X49" t="str">
-            <v xml:space="preserve">q7a1 q7a2 q7b1 q7b2 q7c1 q7c2 q7d1 q7d2 q7e1 q7e2 q7h1 q7h2 q7f1 q7f2 q7g1 q7g2 </v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="V50" t="str">
-            <v/>
-          </cell>
-          <cell r="W50" t="str">
-            <v>q8</v>
-          </cell>
-          <cell r="X50" t="str">
-            <v xml:space="preserve">q81 </v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="V51" t="str">
-            <v>q8</v>
-          </cell>
-          <cell r="W51" t="str">
-            <v>q8</v>
-          </cell>
-          <cell r="X51" t="str">
-            <v xml:space="preserve">q81 q82 </v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="V52" t="str">
-            <v>q9</v>
-          </cell>
-          <cell r="W52" t="str">
-            <v>q9</v>
-          </cell>
-          <cell r="X52" t="str">
-            <v xml:space="preserve">q91 </v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="V53" t="str">
-            <v>q92</v>
-          </cell>
-          <cell r="W53" t="str">
-            <v>q92</v>
-          </cell>
-          <cell r="X53" t="str">
-            <v xml:space="preserve">q92 </v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="V54" t="str">
-            <v>q10</v>
-          </cell>
-          <cell r="W54" t="str">
-            <v>q10</v>
-          </cell>
-          <cell r="X54" t="str">
-            <v xml:space="preserve">q10 </v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="V55" t="str">
-            <v>reg</v>
-          </cell>
-          <cell r="W55" t="str">
-            <v>reg</v>
-          </cell>
-          <cell r="X55" t="str">
-            <v xml:space="preserve">regio </v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="V56" t="str">
-            <v/>
-          </cell>
-          <cell r="W56" t="str">
-            <v/>
-          </cell>
-          <cell r="X56" t="str">
-            <v xml:space="preserve"> </v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="V57" t="str">
-            <v/>
-          </cell>
-          <cell r="W57" t="str">
-            <v/>
-          </cell>
-          <cell r="X57" t="str">
-            <v xml:space="preserve">  </v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="V58" t="str">
-            <v/>
-          </cell>
-          <cell r="W58" t="str">
-            <v/>
-          </cell>
-          <cell r="X58" t="str">
-            <v xml:space="preserve">   </v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="V59" t="str">
-            <v/>
-          </cell>
-          <cell r="W59" t="str">
-            <v/>
-          </cell>
-          <cell r="X59" t="str">
-            <v xml:space="preserve">    </v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="V60" t="str">
-            <v/>
-          </cell>
-          <cell r="W60" t="str">
-            <v/>
-          </cell>
-          <cell r="X60" t="str">
-            <v xml:space="preserve">     </v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="V61" t="str">
-            <v/>
-          </cell>
-          <cell r="W61" t="str">
-            <v/>
-          </cell>
-          <cell r="X61" t="str">
-            <v xml:space="preserve">      </v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="V62" t="str">
-            <v/>
-          </cell>
-          <cell r="W62" t="str">
-            <v/>
-          </cell>
-          <cell r="X62" t="str">
-            <v xml:space="preserve">       </v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="V63" t="str">
-            <v/>
-          </cell>
-          <cell r="W63" t="str">
-            <v/>
-          </cell>
-          <cell r="X63" t="str">
-            <v xml:space="preserve">        </v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="V64" t="str">
-            <v/>
-          </cell>
-          <cell r="W64" t="str">
-            <v/>
-          </cell>
-          <cell r="X64" t="str">
-            <v xml:space="preserve">         </v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="V65" t="str">
-            <v/>
-          </cell>
-          <cell r="W65" t="str">
-            <v/>
-          </cell>
-          <cell r="X65" t="str">
-            <v xml:space="preserve">          </v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="V66" t="str">
-            <v/>
-          </cell>
-          <cell r="W66" t="str">
-            <v/>
-          </cell>
-          <cell r="X66" t="str">
-            <v xml:space="preserve">           </v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="V67" t="str">
-            <v/>
-          </cell>
-          <cell r="W67" t="str">
-            <v/>
-          </cell>
-          <cell r="X67" t="str">
-            <v xml:space="preserve">            </v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="V68" t="str">
-            <v/>
-          </cell>
-          <cell r="W68" t="str">
-            <v/>
-          </cell>
-          <cell r="X68" t="str">
-            <v xml:space="preserve">             </v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="V69" t="str">
-            <v/>
-          </cell>
-          <cell r="W69" t="str">
-            <v/>
-          </cell>
-          <cell r="X69" t="str">
-            <v xml:space="preserve">              </v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="V70" t="str">
-            <v/>
-          </cell>
-          <cell r="W70" t="str">
-            <v/>
-          </cell>
-          <cell r="X70" t="str">
-            <v xml:space="preserve">               </v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="V71" t="str">
-            <v/>
-          </cell>
-          <cell r="W71" t="str">
-            <v/>
-          </cell>
-          <cell r="X71" t="str">
-            <v xml:space="preserve">                </v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="V72" t="str">
-            <v/>
-          </cell>
-          <cell r="W72" t="str">
-            <v/>
-          </cell>
-          <cell r="X72" t="str">
-            <v xml:space="preserve">                 </v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="V73" t="str">
-            <v/>
-          </cell>
-          <cell r="W73" t="str">
-            <v/>
-          </cell>
-          <cell r="X73" t="str">
-            <v xml:space="preserve">                  </v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="V74" t="str">
-            <v/>
-          </cell>
-          <cell r="W74" t="str">
-            <v/>
-          </cell>
-          <cell r="X74" t="str">
-            <v xml:space="preserve">                   </v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="V75" t="str">
-            <v/>
-          </cell>
-          <cell r="W75" t="str">
-            <v/>
-          </cell>
-          <cell r="X75" t="str">
-            <v xml:space="preserve">                    </v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="V76" t="str">
-            <v/>
-          </cell>
-          <cell r="W76" t="str">
-            <v/>
-          </cell>
-          <cell r="X76" t="str">
-            <v xml:space="preserve">                     </v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="V77" t="str">
-            <v/>
-          </cell>
-          <cell r="W77" t="str">
-            <v/>
-          </cell>
-          <cell r="X77" t="str">
-            <v xml:space="preserve">                      </v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="V78" t="str">
-            <v/>
-          </cell>
-          <cell r="W78" t="str">
-            <v/>
-          </cell>
-          <cell r="X78" t="str">
-            <v xml:space="preserve">                       </v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="V79" t="str">
-            <v/>
-          </cell>
-          <cell r="W79" t="str">
-            <v/>
-          </cell>
-          <cell r="X79" t="str">
-            <v xml:space="preserve">                        </v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="V80" t="str">
-            <v/>
-          </cell>
-          <cell r="W80" t="str">
-            <v/>
-          </cell>
-          <cell r="X80" t="str">
-            <v xml:space="preserve">                         </v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="V81" t="str">
-            <v/>
-          </cell>
-          <cell r="W81" t="str">
-            <v/>
-          </cell>
-          <cell r="X81" t="str">
-            <v xml:space="preserve">                          </v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="V82" t="str">
-            <v/>
-          </cell>
-          <cell r="W82" t="str">
-            <v/>
-          </cell>
-          <cell r="X82" t="str">
-            <v xml:space="preserve">                           </v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="V83" t="str">
-            <v/>
-          </cell>
-          <cell r="W83" t="str">
-            <v/>
-          </cell>
-          <cell r="X83" t="str">
-            <v xml:space="preserve">                            </v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="V84" t="str">
-            <v/>
-          </cell>
-          <cell r="W84" t="str">
-            <v/>
-          </cell>
-          <cell r="X84" t="str">
-            <v xml:space="preserve">                             </v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="V85" t="str">
-            <v/>
-          </cell>
-          <cell r="W85" t="str">
-            <v/>
-          </cell>
-          <cell r="X85" t="str">
-            <v xml:space="preserve">                              </v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="V86" t="str">
-            <v/>
-          </cell>
-          <cell r="W86" t="str">
-            <v/>
-          </cell>
-          <cell r="X86" t="str">
-            <v xml:space="preserve">                               </v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="V87" t="str">
-            <v/>
-          </cell>
-          <cell r="W87" t="str">
-            <v/>
-          </cell>
-          <cell r="X87" t="str">
-            <v xml:space="preserve">                                </v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="V88" t="str">
-            <v/>
-          </cell>
-          <cell r="W88" t="str">
-            <v/>
-          </cell>
-          <cell r="X88" t="str">
-            <v xml:space="preserve">                                 </v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="V89" t="str">
-            <v/>
-          </cell>
-          <cell r="W89" t="str">
-            <v/>
-          </cell>
-          <cell r="X89" t="str">
-            <v xml:space="preserve">                                  </v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="V90" t="str">
-            <v/>
-          </cell>
-          <cell r="W90" t="str">
-            <v/>
-          </cell>
-          <cell r="X90" t="str">
-            <v xml:space="preserve">                                   </v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="V91" t="str">
-            <v/>
-          </cell>
-          <cell r="W91" t="str">
-            <v/>
-          </cell>
-          <cell r="X91" t="str">
-            <v xml:space="preserve">                                    </v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="V92" t="str">
-            <v/>
-          </cell>
-          <cell r="W92" t="str">
-            <v/>
-          </cell>
-          <cell r="X92" t="str">
-            <v xml:space="preserve">                                     </v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="V93" t="str">
-            <v/>
-          </cell>
-          <cell r="W93" t="str">
-            <v/>
-          </cell>
-          <cell r="X93" t="str">
-            <v xml:space="preserve">                                      </v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="V94" t="str">
-            <v/>
-          </cell>
-          <cell r="W94" t="str">
-            <v/>
-          </cell>
-          <cell r="X94" t="str">
-            <v xml:space="preserve">                                       </v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="V95" t="str">
-            <v/>
-          </cell>
-          <cell r="W95" t="str">
-            <v/>
-          </cell>
-          <cell r="X95" t="str">
-            <v xml:space="preserve">                                        </v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="V96" t="str">
-            <v/>
-          </cell>
-          <cell r="W96" t="str">
-            <v/>
-          </cell>
-          <cell r="X96" t="str">
-            <v xml:space="preserve">                                         </v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="V97" t="str">
-            <v/>
-          </cell>
-          <cell r="W97" t="str">
-            <v/>
-          </cell>
-          <cell r="X97" t="str">
-            <v xml:space="preserve">                                          </v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="V98" t="str">
-            <v/>
-          </cell>
-          <cell r="W98" t="str">
-            <v/>
-          </cell>
-          <cell r="X98" t="str">
-            <v xml:space="preserve">                                           </v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="V99" t="str">
-            <v/>
-          </cell>
-          <cell r="W99" t="str">
-            <v/>
-          </cell>
-          <cell r="X99" t="str">
-            <v xml:space="preserve">                                            </v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="V100" t="str">
-            <v/>
-          </cell>
-          <cell r="W100" t="str">
-            <v/>
-          </cell>
-          <cell r="X100" t="str">
-            <v xml:space="preserve">                                             </v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="V101" t="str">
-            <v/>
-          </cell>
-          <cell r="W101" t="str">
-            <v/>
-          </cell>
-          <cell r="X101" t="str">
-            <v xml:space="preserve">                                              </v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="V102" t="str">
-            <v/>
-          </cell>
-          <cell r="W102" t="str">
-            <v/>
-          </cell>
-          <cell r="X102" t="str">
-            <v xml:space="preserve">                                               </v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="V103" t="str">
-            <v/>
-          </cell>
-          <cell r="W103" t="str">
-            <v/>
-          </cell>
-          <cell r="X103" t="str">
-            <v xml:space="preserve">                                                </v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="V104" t="str">
-            <v/>
-          </cell>
-          <cell r="W104" t="str">
-            <v/>
-          </cell>
-          <cell r="X104" t="str">
-            <v xml:space="preserve">                                                 </v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="V105" t="str">
-            <v/>
-          </cell>
-          <cell r="W105" t="str">
-            <v/>
-          </cell>
-          <cell r="X105" t="str">
-            <v xml:space="preserve">                                                  </v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="V106" t="str">
-            <v/>
-          </cell>
-          <cell r="W106" t="str">
-            <v/>
-          </cell>
-          <cell r="X106" t="str">
-            <v xml:space="preserve">                                                   </v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="V107" t="str">
-            <v/>
-          </cell>
-          <cell r="W107" t="str">
-            <v/>
-          </cell>
-          <cell r="X107" t="str">
-            <v xml:space="preserve">                                                    </v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="V108" t="str">
-            <v/>
-          </cell>
-          <cell r="W108" t="str">
-            <v/>
-          </cell>
-          <cell r="X108" t="str">
-            <v xml:space="preserve">                                                     </v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="V109" t="str">
-            <v/>
-          </cell>
-          <cell r="W109" t="str">
-            <v/>
-          </cell>
-          <cell r="X109" t="str">
-            <v xml:space="preserve">                                                      </v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="V110" t="str">
-            <v/>
-          </cell>
-          <cell r="W110" t="str">
-            <v/>
-          </cell>
-          <cell r="X110" t="str">
-            <v xml:space="preserve">                                                       </v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="V111" t="str">
-            <v/>
-          </cell>
-          <cell r="W111" t="str">
-            <v/>
-          </cell>
-          <cell r="X111" t="str">
-            <v xml:space="preserve">                                                        </v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="V112" t="str">
-            <v/>
-          </cell>
-          <cell r="W112" t="str">
-            <v/>
-          </cell>
-          <cell r="X112" t="str">
-            <v xml:space="preserve">                                                         </v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="V113" t="str">
-            <v/>
-          </cell>
-          <cell r="W113" t="str">
-            <v/>
-          </cell>
-          <cell r="X113" t="str">
-            <v xml:space="preserve">                                                          </v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="V114" t="str">
-            <v/>
-          </cell>
-          <cell r="W114" t="str">
-            <v/>
-          </cell>
-          <cell r="X114" t="str">
-            <v xml:space="preserve">                                                           </v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="V115" t="str">
-            <v/>
-          </cell>
-          <cell r="W115" t="str">
-            <v/>
-          </cell>
-          <cell r="X115" t="str">
-            <v xml:space="preserve">                                                            </v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="V116" t="str">
-            <v/>
-          </cell>
-          <cell r="W116" t="str">
-            <v/>
-          </cell>
-          <cell r="X116" t="str">
-            <v xml:space="preserve">                                                             </v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="V117" t="str">
-            <v/>
-          </cell>
-          <cell r="W117" t="str">
-            <v/>
-          </cell>
-          <cell r="X117" t="str">
-            <v xml:space="preserve">                                                              </v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="V118" t="str">
-            <v/>
-          </cell>
-          <cell r="W118" t="str">
-            <v/>
-          </cell>
-          <cell r="X118" t="str">
-            <v xml:space="preserve">                                                               </v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="V119" t="str">
-            <v/>
-          </cell>
-          <cell r="W119" t="str">
-            <v/>
-          </cell>
-          <cell r="X119" t="str">
-            <v xml:space="preserve">                                                                </v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="V120" t="str">
-            <v/>
-          </cell>
-          <cell r="W120" t="str">
-            <v/>
-          </cell>
-          <cell r="X120" t="str">
-            <v xml:space="preserve">                                                                 </v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="V121" t="str">
-            <v/>
-          </cell>
-          <cell r="W121" t="str">
-            <v/>
-          </cell>
-          <cell r="X121" t="str">
-            <v xml:space="preserve">                                                                  </v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="V122" t="str">
-            <v/>
-          </cell>
-          <cell r="W122" t="str">
-            <v/>
-          </cell>
-          <cell r="X122" t="str">
-            <v xml:space="preserve">                                                                   </v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="V123" t="str">
-            <v/>
-          </cell>
-          <cell r="W123" t="str">
-            <v/>
-          </cell>
-          <cell r="X123" t="str">
-            <v xml:space="preserve">                                                                    </v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="V124" t="str">
-            <v/>
-          </cell>
-          <cell r="W124" t="str">
-            <v/>
-          </cell>
-          <cell r="X124" t="str">
-            <v xml:space="preserve">                                                                     </v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="V125" t="str">
-            <v/>
-          </cell>
-          <cell r="W125" t="str">
-            <v/>
-          </cell>
-          <cell r="X125" t="str">
-            <v xml:space="preserve">                                                                      </v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="V126" t="str">
-            <v/>
-          </cell>
-          <cell r="W126" t="str">
-            <v/>
-          </cell>
-          <cell r="X126" t="str">
-            <v xml:space="preserve">                                                                       </v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="V127" t="str">
-            <v/>
-          </cell>
-          <cell r="W127" t="str">
-            <v/>
-          </cell>
-          <cell r="X127" t="str">
-            <v xml:space="preserve">                                                                        </v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="V128" t="str">
-            <v/>
-          </cell>
-          <cell r="W128" t="str">
-            <v/>
-          </cell>
-          <cell r="X128" t="str">
-            <v xml:space="preserve">                                                                         </v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="V129" t="str">
-            <v/>
-          </cell>
-          <cell r="W129" t="str">
-            <v/>
-          </cell>
-          <cell r="X129" t="str">
-            <v xml:space="preserve">                                                                          </v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="V130" t="str">
-            <v/>
-          </cell>
-          <cell r="W130" t="str">
-            <v/>
-          </cell>
-          <cell r="X130" t="str">
-            <v xml:space="preserve">                                                                           </v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="V131" t="str">
-            <v/>
-          </cell>
-          <cell r="W131" t="str">
-            <v/>
-          </cell>
-          <cell r="X131" t="str">
-            <v xml:space="preserve">                                                                            </v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="V132" t="str">
-            <v/>
-          </cell>
-          <cell r="W132" t="str">
-            <v/>
-          </cell>
-          <cell r="X132" t="str">
-            <v xml:space="preserve">                                                                             </v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="V133" t="str">
-            <v/>
-          </cell>
-          <cell r="W133" t="str">
-            <v/>
-          </cell>
-          <cell r="X133" t="str">
-            <v xml:space="preserve">                                                                              </v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="V134" t="str">
-            <v/>
-          </cell>
-          <cell r="W134" t="str">
-            <v/>
-          </cell>
-          <cell r="X134" t="str">
-            <v xml:space="preserve">                                                                               </v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="V135" t="str">
-            <v/>
-          </cell>
-          <cell r="W135" t="str">
-            <v/>
-          </cell>
-          <cell r="X135" t="str">
-            <v xml:space="preserve">                                                                                </v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="V136" t="str">
-            <v/>
-          </cell>
-          <cell r="W136" t="str">
-            <v/>
-          </cell>
-          <cell r="X136" t="str">
-            <v xml:space="preserve">                                                                                 </v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="V137" t="str">
-            <v/>
-          </cell>
-          <cell r="W137" t="str">
-            <v/>
-          </cell>
-          <cell r="X137" t="str">
-            <v xml:space="preserve">                                                                                  </v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="V138" t="str">
-            <v/>
-          </cell>
-          <cell r="W138" t="str">
-            <v/>
-          </cell>
-          <cell r="X138" t="str">
-            <v xml:space="preserve">                                                                                   </v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="V139" t="str">
-            <v/>
-          </cell>
-          <cell r="W139" t="str">
-            <v/>
-          </cell>
-          <cell r="X139" t="str">
-            <v xml:space="preserve">                                                                                    </v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="V140" t="str">
-            <v/>
-          </cell>
-          <cell r="W140" t="str">
-            <v/>
-          </cell>
-          <cell r="X140" t="str">
-            <v xml:space="preserve">                                                                                     </v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="V141" t="str">
-            <v/>
-          </cell>
-          <cell r="W141" t="str">
-            <v/>
-          </cell>
-          <cell r="X141" t="str">
-            <v xml:space="preserve">                                                                                      </v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="V142" t="str">
-            <v/>
-          </cell>
-          <cell r="W142" t="str">
-            <v/>
-          </cell>
-          <cell r="X142" t="str">
-            <v xml:space="preserve">                                                                                       </v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="V143" t="str">
-            <v/>
-          </cell>
-          <cell r="W143" t="str">
-            <v/>
-          </cell>
-          <cell r="X143" t="str">
-            <v xml:space="preserve">                                                                                        </v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="V144" t="str">
-            <v/>
-          </cell>
-          <cell r="W144" t="str">
-            <v/>
-          </cell>
-          <cell r="X144" t="str">
-            <v xml:space="preserve">                                                                                         </v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="V145" t="str">
-            <v/>
-          </cell>
-          <cell r="W145" t="str">
-            <v/>
-          </cell>
-          <cell r="X145" t="str">
-            <v xml:space="preserve">                                                                                          </v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="V146" t="str">
-            <v/>
-          </cell>
-          <cell r="W146" t="str">
-            <v/>
-          </cell>
-          <cell r="X146" t="str">
-            <v xml:space="preserve">                                                                                           </v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="V147" t="str">
-            <v/>
-          </cell>
-          <cell r="W147" t="str">
-            <v/>
-          </cell>
-          <cell r="X147" t="str">
-            <v xml:space="preserve">                                                                                            </v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="V148" t="str">
-            <v/>
-          </cell>
-          <cell r="W148" t="str">
-            <v/>
-          </cell>
-          <cell r="X148" t="str">
-            <v xml:space="preserve">                                                                                             </v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="V149" t="str">
-            <v/>
-          </cell>
-          <cell r="W149" t="str">
-            <v/>
-          </cell>
-          <cell r="X149" t="str">
-            <v xml:space="preserve">                                                                                              </v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="V150" t="str">
-            <v/>
-          </cell>
-          <cell r="W150" t="str">
-            <v/>
-          </cell>
-          <cell r="X150" t="str">
-            <v xml:space="preserve">                                                                                               </v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="V151" t="str">
-            <v/>
-          </cell>
-          <cell r="W151" t="str">
-            <v/>
-          </cell>
-          <cell r="X151" t="str">
-            <v xml:space="preserve">                                                                                                </v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="V152" t="str">
-            <v/>
-          </cell>
-          <cell r="W152" t="str">
-            <v/>
-          </cell>
-          <cell r="X152" t="str">
-            <v xml:space="preserve">                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="V153" t="str">
-            <v/>
-          </cell>
-          <cell r="W153" t="str">
-            <v/>
-          </cell>
-          <cell r="X153" t="str">
-            <v xml:space="preserve">                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="V154" t="str">
-            <v/>
-          </cell>
-          <cell r="W154" t="str">
-            <v/>
-          </cell>
-          <cell r="X154" t="str">
-            <v xml:space="preserve">                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="V155" t="str">
-            <v/>
-          </cell>
-          <cell r="W155" t="str">
-            <v/>
-          </cell>
-          <cell r="X155" t="str">
-            <v xml:space="preserve">                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="V156" t="str">
-            <v/>
-          </cell>
-          <cell r="W156" t="str">
-            <v/>
-          </cell>
-          <cell r="X156" t="str">
-            <v xml:space="preserve">                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="V157" t="str">
-            <v/>
-          </cell>
-          <cell r="W157" t="str">
-            <v/>
-          </cell>
-          <cell r="X157" t="str">
-            <v xml:space="preserve">                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="V158" t="str">
-            <v/>
-          </cell>
-          <cell r="W158" t="str">
-            <v/>
-          </cell>
-          <cell r="X158" t="str">
-            <v xml:space="preserve">                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="V159" t="str">
-            <v/>
-          </cell>
-          <cell r="W159" t="str">
-            <v/>
-          </cell>
-          <cell r="X159" t="str">
-            <v xml:space="preserve">                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="V160" t="str">
-            <v/>
-          </cell>
-          <cell r="W160" t="str">
-            <v/>
-          </cell>
-          <cell r="X160" t="str">
-            <v xml:space="preserve">                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="V161" t="str">
-            <v/>
-          </cell>
-          <cell r="W161" t="str">
-            <v/>
-          </cell>
-          <cell r="X161" t="str">
-            <v xml:space="preserve">                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="V162" t="str">
-            <v/>
-          </cell>
-          <cell r="W162" t="str">
-            <v/>
-          </cell>
-          <cell r="X162" t="str">
-            <v xml:space="preserve">                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="V163" t="str">
-            <v/>
-          </cell>
-          <cell r="W163" t="str">
-            <v/>
-          </cell>
-          <cell r="X163" t="str">
-            <v xml:space="preserve">                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="V164" t="str">
-            <v/>
-          </cell>
-          <cell r="W164" t="str">
-            <v/>
-          </cell>
-          <cell r="X164" t="str">
-            <v xml:space="preserve">                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="V165" t="str">
-            <v/>
-          </cell>
-          <cell r="W165" t="str">
-            <v/>
-          </cell>
-          <cell r="X165" t="str">
-            <v xml:space="preserve">                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="V166" t="str">
-            <v/>
-          </cell>
-          <cell r="W166" t="str">
-            <v/>
-          </cell>
-          <cell r="X166" t="str">
-            <v xml:space="preserve">                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="V167" t="str">
-            <v/>
-          </cell>
-          <cell r="W167" t="str">
-            <v/>
-          </cell>
-          <cell r="X167" t="str">
-            <v xml:space="preserve">                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="V168" t="str">
-            <v/>
-          </cell>
-          <cell r="W168" t="str">
-            <v/>
-          </cell>
-          <cell r="X168" t="str">
-            <v xml:space="preserve">                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="V169" t="str">
-            <v/>
-          </cell>
-          <cell r="W169" t="str">
-            <v/>
-          </cell>
-          <cell r="X169" t="str">
-            <v xml:space="preserve">                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="V170" t="str">
-            <v/>
-          </cell>
-          <cell r="W170" t="str">
-            <v/>
-          </cell>
-          <cell r="X170" t="str">
-            <v xml:space="preserve">                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="V171" t="str">
-            <v/>
-          </cell>
-          <cell r="W171" t="str">
-            <v/>
-          </cell>
-          <cell r="X171" t="str">
-            <v xml:space="preserve">                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="V172" t="str">
-            <v/>
-          </cell>
-          <cell r="W172" t="str">
-            <v/>
-          </cell>
-          <cell r="X172" t="str">
-            <v xml:space="preserve">                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="V173" t="str">
-            <v/>
-          </cell>
-          <cell r="W173" t="str">
-            <v/>
-          </cell>
-          <cell r="X173" t="str">
-            <v xml:space="preserve">                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="V174" t="str">
-            <v/>
-          </cell>
-          <cell r="W174" t="str">
-            <v/>
-          </cell>
-          <cell r="X174" t="str">
-            <v xml:space="preserve">                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="V175" t="str">
-            <v/>
-          </cell>
-          <cell r="W175" t="str">
-            <v/>
-          </cell>
-          <cell r="X175" t="str">
-            <v xml:space="preserve">                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="V176" t="str">
-            <v/>
-          </cell>
-          <cell r="W176" t="str">
-            <v/>
-          </cell>
-          <cell r="X176" t="str">
-            <v xml:space="preserve">                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="V177" t="str">
-            <v/>
-          </cell>
-          <cell r="W177" t="str">
-            <v/>
-          </cell>
-          <cell r="X177" t="str">
-            <v xml:space="preserve">                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="V178" t="str">
-            <v/>
-          </cell>
-          <cell r="W178" t="str">
-            <v/>
-          </cell>
-          <cell r="X178" t="str">
-            <v xml:space="preserve">                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="V179" t="str">
-            <v/>
-          </cell>
-          <cell r="W179" t="str">
-            <v/>
-          </cell>
-          <cell r="X179" t="str">
-            <v xml:space="preserve">                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="V180" t="str">
-            <v/>
-          </cell>
-          <cell r="W180" t="str">
-            <v/>
-          </cell>
-          <cell r="X180" t="str">
-            <v xml:space="preserve">                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="V181" t="str">
-            <v/>
-          </cell>
-          <cell r="W181" t="str">
-            <v/>
-          </cell>
-          <cell r="X181" t="str">
-            <v xml:space="preserve">                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="V182" t="str">
-            <v/>
-          </cell>
-          <cell r="W182" t="str">
-            <v/>
-          </cell>
-          <cell r="X182" t="str">
-            <v xml:space="preserve">                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="V183" t="str">
-            <v/>
-          </cell>
-          <cell r="W183" t="str">
-            <v/>
-          </cell>
-          <cell r="X183" t="str">
-            <v xml:space="preserve">                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="V184" t="str">
-            <v/>
-          </cell>
-          <cell r="W184" t="str">
-            <v/>
-          </cell>
-          <cell r="X184" t="str">
-            <v xml:space="preserve">                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="V185" t="str">
-            <v/>
-          </cell>
-          <cell r="W185" t="str">
-            <v/>
-          </cell>
-          <cell r="X185" t="str">
-            <v xml:space="preserve">                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="V186" t="str">
-            <v/>
-          </cell>
-          <cell r="W186" t="str">
-            <v/>
-          </cell>
-          <cell r="X186" t="str">
-            <v xml:space="preserve">                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="V187" t="str">
-            <v/>
-          </cell>
-          <cell r="W187" t="str">
-            <v/>
-          </cell>
-          <cell r="X187" t="str">
-            <v xml:space="preserve">                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="V188" t="str">
-            <v/>
-          </cell>
-          <cell r="W188" t="str">
-            <v/>
-          </cell>
-          <cell r="X188" t="str">
-            <v xml:space="preserve">                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="V189" t="str">
-            <v/>
-          </cell>
-          <cell r="W189" t="str">
-            <v/>
-          </cell>
-          <cell r="X189" t="str">
-            <v xml:space="preserve">                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="V190" t="str">
-            <v/>
-          </cell>
-          <cell r="W190" t="str">
-            <v/>
-          </cell>
-          <cell r="X190" t="str">
-            <v xml:space="preserve">                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="V191" t="str">
-            <v/>
-          </cell>
-          <cell r="W191" t="str">
-            <v/>
-          </cell>
-          <cell r="X191" t="str">
-            <v xml:space="preserve">                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="V192" t="str">
-            <v/>
-          </cell>
-          <cell r="W192" t="str">
-            <v/>
-          </cell>
-          <cell r="X192" t="str">
-            <v xml:space="preserve">                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="V193" t="str">
-            <v/>
-          </cell>
-          <cell r="W193" t="str">
-            <v/>
-          </cell>
-          <cell r="X193" t="str">
-            <v xml:space="preserve">                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="V194" t="str">
-            <v/>
-          </cell>
-          <cell r="W194" t="str">
-            <v/>
-          </cell>
-          <cell r="X194" t="str">
-            <v xml:space="preserve">                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="V195" t="str">
-            <v/>
-          </cell>
-          <cell r="W195" t="str">
-            <v/>
-          </cell>
-          <cell r="X195" t="str">
-            <v xml:space="preserve">                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="V196" t="str">
-            <v/>
-          </cell>
-          <cell r="W196" t="str">
-            <v/>
-          </cell>
-          <cell r="X196" t="str">
-            <v xml:space="preserve">                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="V197" t="str">
-            <v/>
-          </cell>
-          <cell r="W197" t="str">
-            <v/>
-          </cell>
-          <cell r="X197" t="str">
-            <v xml:space="preserve">                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="V198" t="str">
-            <v/>
-          </cell>
-          <cell r="W198" t="str">
-            <v/>
-          </cell>
-          <cell r="X198" t="str">
-            <v xml:space="preserve">                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="V199" t="str">
-            <v/>
-          </cell>
-          <cell r="W199" t="str">
-            <v/>
-          </cell>
-          <cell r="X199" t="str">
-            <v xml:space="preserve">                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="V200" t="str">
-            <v/>
-          </cell>
-          <cell r="W200" t="str">
-            <v/>
-          </cell>
-          <cell r="X200" t="str">
-            <v xml:space="preserve">                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="V201" t="str">
-            <v/>
-          </cell>
-          <cell r="W201" t="str">
-            <v/>
-          </cell>
-          <cell r="X201" t="str">
-            <v xml:space="preserve">                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="V202" t="str">
-            <v/>
-          </cell>
-          <cell r="W202" t="str">
-            <v/>
-          </cell>
-          <cell r="X202" t="str">
-            <v xml:space="preserve">                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="V203" t="str">
-            <v/>
-          </cell>
-          <cell r="W203" t="str">
-            <v/>
-          </cell>
-          <cell r="X203" t="str">
-            <v xml:space="preserve">                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="V204" t="str">
-            <v/>
-          </cell>
-          <cell r="W204" t="str">
-            <v/>
-          </cell>
-          <cell r="X204" t="str">
-            <v xml:space="preserve">                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="V205" t="str">
-            <v/>
-          </cell>
-          <cell r="W205" t="str">
-            <v/>
-          </cell>
-          <cell r="X205" t="str">
-            <v xml:space="preserve">                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="V206" t="str">
-            <v/>
-          </cell>
-          <cell r="W206" t="str">
-            <v/>
-          </cell>
-          <cell r="X206" t="str">
-            <v xml:space="preserve">                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="V207" t="str">
-            <v/>
-          </cell>
-          <cell r="W207" t="str">
-            <v/>
-          </cell>
-          <cell r="X207" t="str">
-            <v xml:space="preserve">                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="V208" t="str">
-            <v/>
-          </cell>
-          <cell r="W208" t="str">
-            <v/>
-          </cell>
-          <cell r="X208" t="str">
-            <v xml:space="preserve">                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="V209" t="str">
-            <v/>
-          </cell>
-          <cell r="W209" t="str">
-            <v/>
-          </cell>
-          <cell r="X209" t="str">
-            <v xml:space="preserve">                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="V210" t="str">
-            <v/>
-          </cell>
-          <cell r="W210" t="str">
-            <v/>
-          </cell>
-          <cell r="X210" t="str">
-            <v xml:space="preserve">                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="V211" t="str">
-            <v/>
-          </cell>
-          <cell r="W211" t="str">
-            <v/>
-          </cell>
-          <cell r="X211" t="str">
-            <v xml:space="preserve">                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="V212" t="str">
-            <v/>
-          </cell>
-          <cell r="W212" t="str">
-            <v/>
-          </cell>
-          <cell r="X212" t="str">
-            <v xml:space="preserve">                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="V213" t="str">
-            <v/>
-          </cell>
-          <cell r="W213" t="str">
-            <v/>
-          </cell>
-          <cell r="X213" t="str">
-            <v xml:space="preserve">                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="V214" t="str">
-            <v/>
-          </cell>
-          <cell r="W214" t="str">
-            <v/>
-          </cell>
-          <cell r="X214" t="str">
-            <v xml:space="preserve">                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="V215" t="str">
-            <v/>
-          </cell>
-          <cell r="W215" t="str">
-            <v/>
-          </cell>
-          <cell r="X215" t="str">
-            <v xml:space="preserve">                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="V216" t="str">
-            <v/>
-          </cell>
-          <cell r="W216" t="str">
-            <v/>
-          </cell>
-          <cell r="X216" t="str">
-            <v xml:space="preserve">                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="V217" t="str">
-            <v/>
-          </cell>
-          <cell r="W217" t="str">
-            <v/>
-          </cell>
-          <cell r="X217" t="str">
-            <v xml:space="preserve">                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="V218" t="str">
-            <v/>
-          </cell>
-          <cell r="W218" t="str">
-            <v/>
-          </cell>
-          <cell r="X218" t="str">
-            <v xml:space="preserve">                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="V219" t="str">
-            <v/>
-          </cell>
-          <cell r="W219" t="str">
-            <v/>
-          </cell>
-          <cell r="X219" t="str">
-            <v xml:space="preserve">                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="V220" t="str">
-            <v/>
-          </cell>
-          <cell r="W220" t="str">
-            <v/>
-          </cell>
-          <cell r="X220" t="str">
-            <v xml:space="preserve">                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="V221" t="str">
-            <v/>
-          </cell>
-          <cell r="W221" t="str">
-            <v/>
-          </cell>
-          <cell r="X221" t="str">
-            <v xml:space="preserve">                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="V222" t="str">
-            <v/>
-          </cell>
-          <cell r="W222" t="str">
-            <v/>
-          </cell>
-          <cell r="X222" t="str">
-            <v xml:space="preserve">                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="V223" t="str">
-            <v/>
-          </cell>
-          <cell r="W223" t="str">
-            <v/>
-          </cell>
-          <cell r="X223" t="str">
-            <v xml:space="preserve">                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="V224" t="str">
-            <v/>
-          </cell>
-          <cell r="W224" t="str">
-            <v/>
-          </cell>
-          <cell r="X224" t="str">
-            <v xml:space="preserve">                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="V225" t="str">
-            <v/>
-          </cell>
-          <cell r="W225" t="str">
-            <v/>
-          </cell>
-          <cell r="X225" t="str">
-            <v xml:space="preserve">                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="V226" t="str">
-            <v/>
-          </cell>
-          <cell r="W226" t="str">
-            <v/>
-          </cell>
-          <cell r="X226" t="str">
-            <v xml:space="preserve">                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="V227" t="str">
-            <v/>
-          </cell>
-          <cell r="W227" t="str">
-            <v/>
-          </cell>
-          <cell r="X227" t="str">
-            <v xml:space="preserve">                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="V228" t="str">
-            <v/>
-          </cell>
-          <cell r="W228" t="str">
-            <v/>
-          </cell>
-          <cell r="X228" t="str">
-            <v xml:space="preserve">                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="V229" t="str">
-            <v/>
-          </cell>
-          <cell r="W229" t="str">
-            <v/>
-          </cell>
-          <cell r="X229" t="str">
-            <v xml:space="preserve">                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="V230" t="str">
-            <v/>
-          </cell>
-          <cell r="W230" t="str">
-            <v/>
-          </cell>
-          <cell r="X230" t="str">
-            <v xml:space="preserve">                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="V231" t="str">
-            <v/>
-          </cell>
-          <cell r="W231" t="str">
-            <v/>
-          </cell>
-          <cell r="X231" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="V232" t="str">
-            <v/>
-          </cell>
-          <cell r="W232" t="str">
-            <v/>
-          </cell>
-          <cell r="X232" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="V233" t="str">
-            <v/>
-          </cell>
-          <cell r="W233" t="str">
-            <v/>
-          </cell>
-          <cell r="X233" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="V234" t="str">
-            <v/>
-          </cell>
-          <cell r="W234" t="str">
-            <v/>
-          </cell>
-          <cell r="X234" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="V235" t="str">
-            <v/>
-          </cell>
-          <cell r="W235" t="str">
-            <v/>
-          </cell>
-          <cell r="X235" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="V236" t="str">
-            <v/>
-          </cell>
-          <cell r="W236" t="str">
-            <v/>
-          </cell>
-          <cell r="X236" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="237">
-          <cell r="V237" t="str">
-            <v/>
-          </cell>
-          <cell r="W237" t="str">
-            <v/>
-          </cell>
-          <cell r="X237" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="238">
-          <cell r="V238" t="str">
-            <v/>
-          </cell>
-          <cell r="W238" t="str">
-            <v/>
-          </cell>
-          <cell r="X238" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="239">
-          <cell r="V239" t="str">
-            <v/>
-          </cell>
-          <cell r="W239" t="str">
-            <v/>
-          </cell>
-          <cell r="X239" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="V240" t="str">
-            <v/>
-          </cell>
-          <cell r="W240" t="str">
-            <v/>
-          </cell>
-          <cell r="X240" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="V241" t="str">
-            <v/>
-          </cell>
-          <cell r="W241" t="str">
-            <v/>
-          </cell>
-          <cell r="X241" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="V242" t="str">
-            <v/>
-          </cell>
-          <cell r="W242" t="str">
-            <v/>
-          </cell>
-          <cell r="X242" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="V243" t="str">
-            <v/>
-          </cell>
-          <cell r="W243" t="str">
-            <v/>
-          </cell>
-          <cell r="X243" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="244">
-          <cell r="V244" t="str">
-            <v/>
-          </cell>
-          <cell r="W244" t="str">
-            <v/>
-          </cell>
-          <cell r="X244" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="245">
-          <cell r="V245" t="str">
-            <v/>
-          </cell>
-          <cell r="W245" t="str">
-            <v/>
-          </cell>
-          <cell r="X245" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="246">
-          <cell r="V246" t="str">
-            <v/>
-          </cell>
-          <cell r="W246" t="str">
-            <v/>
-          </cell>
-          <cell r="X246" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="247">
-          <cell r="V247" t="str">
-            <v/>
-          </cell>
-          <cell r="W247" t="str">
-            <v/>
-          </cell>
-          <cell r="X247" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="V248" t="str">
-            <v/>
-          </cell>
-          <cell r="W248" t="str">
-            <v/>
-          </cell>
-          <cell r="X248" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="249">
-          <cell r="V249" t="str">
-            <v/>
-          </cell>
-          <cell r="W249" t="str">
-            <v/>
-          </cell>
-          <cell r="X249" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="250">
-          <cell r="V250" t="str">
-            <v/>
-          </cell>
-          <cell r="W250" t="str">
-            <v/>
-          </cell>
-          <cell r="X250" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="251">
-          <cell r="V251" t="str">
-            <v/>
-          </cell>
-          <cell r="W251" t="str">
-            <v/>
-          </cell>
-          <cell r="X251" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="252">
-          <cell r="V252" t="str">
-            <v/>
-          </cell>
-          <cell r="W252" t="str">
-            <v/>
-          </cell>
-          <cell r="X252" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="253">
-          <cell r="V253" t="str">
-            <v/>
-          </cell>
-          <cell r="W253" t="str">
-            <v/>
-          </cell>
-          <cell r="X253" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="254">
-          <cell r="V254" t="str">
-            <v/>
-          </cell>
-          <cell r="W254" t="str">
-            <v/>
-          </cell>
-          <cell r="X254" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="255">
-          <cell r="V255" t="str">
-            <v/>
-          </cell>
-          <cell r="W255" t="str">
-            <v/>
-          </cell>
-          <cell r="X255" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="256">
-          <cell r="V256" t="str">
-            <v/>
-          </cell>
-          <cell r="W256" t="str">
-            <v/>
-          </cell>
-          <cell r="X256" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="257">
-          <cell r="V257" t="str">
-            <v/>
-          </cell>
-          <cell r="W257" t="str">
-            <v/>
-          </cell>
-          <cell r="X257" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="258">
-          <cell r="V258" t="str">
-            <v/>
-          </cell>
-          <cell r="W258" t="str">
-            <v/>
-          </cell>
-          <cell r="X258" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="259">
-          <cell r="V259" t="str">
-            <v/>
-          </cell>
-          <cell r="W259" t="str">
-            <v/>
-          </cell>
-          <cell r="X259" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="260">
-          <cell r="V260" t="str">
-            <v/>
-          </cell>
-          <cell r="W260" t="str">
-            <v/>
-          </cell>
-          <cell r="X260" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="261">
-          <cell r="V261" t="str">
-            <v/>
-          </cell>
-          <cell r="W261" t="str">
-            <v/>
-          </cell>
-          <cell r="X261" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="262">
-          <cell r="V262" t="str">
-            <v/>
-          </cell>
-          <cell r="W262" t="str">
-            <v/>
-          </cell>
-          <cell r="X262" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="263">
-          <cell r="V263" t="str">
-            <v/>
-          </cell>
-          <cell r="W263" t="str">
-            <v/>
-          </cell>
-          <cell r="X263" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="264">
-          <cell r="V264" t="str">
-            <v/>
-          </cell>
-          <cell r="W264" t="str">
-            <v/>
-          </cell>
-          <cell r="X264" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="265">
-          <cell r="V265" t="str">
-            <v/>
-          </cell>
-          <cell r="W265" t="str">
-            <v/>
-          </cell>
-          <cell r="X265" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="266">
-          <cell r="V266" t="str">
-            <v/>
-          </cell>
-          <cell r="W266" t="str">
-            <v/>
-          </cell>
-          <cell r="X266" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="267">
-          <cell r="V267" t="str">
-            <v/>
-          </cell>
-          <cell r="W267" t="str">
-            <v/>
-          </cell>
-          <cell r="X267" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="268">
-          <cell r="V268" t="str">
-            <v/>
-          </cell>
-          <cell r="W268" t="str">
-            <v/>
-          </cell>
-          <cell r="X268" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="269">
-          <cell r="V269" t="str">
-            <v/>
-          </cell>
-          <cell r="W269" t="str">
-            <v/>
-          </cell>
-          <cell r="X269" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="270">
-          <cell r="V270" t="str">
-            <v/>
-          </cell>
-          <cell r="W270" t="str">
-            <v/>
-          </cell>
-          <cell r="X270" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="271">
-          <cell r="V271" t="str">
-            <v/>
-          </cell>
-          <cell r="W271" t="str">
-            <v/>
-          </cell>
-          <cell r="X271" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="272">
-          <cell r="V272" t="str">
-            <v/>
-          </cell>
-          <cell r="W272" t="str">
-            <v/>
-          </cell>
-          <cell r="X272" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="273">
-          <cell r="V273" t="str">
-            <v/>
-          </cell>
-          <cell r="W273" t="str">
-            <v/>
-          </cell>
-          <cell r="X273" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="274">
-          <cell r="V274" t="str">
-            <v/>
-          </cell>
-          <cell r="W274" t="str">
-            <v/>
-          </cell>
-          <cell r="X274" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="275">
-          <cell r="V275" t="str">
-            <v/>
-          </cell>
-          <cell r="W275" t="str">
-            <v/>
-          </cell>
-          <cell r="X275" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="276">
-          <cell r="V276" t="str">
-            <v/>
-          </cell>
-          <cell r="W276" t="str">
-            <v/>
-          </cell>
-          <cell r="X276" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="277">
-          <cell r="V277" t="str">
-            <v/>
-          </cell>
-          <cell r="W277" t="str">
-            <v/>
-          </cell>
-          <cell r="X277" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="278">
-          <cell r="V278" t="str">
-            <v/>
-          </cell>
-          <cell r="W278" t="str">
-            <v/>
-          </cell>
-          <cell r="X278" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="279">
-          <cell r="V279" t="str">
-            <v/>
-          </cell>
-          <cell r="W279" t="str">
-            <v/>
-          </cell>
-          <cell r="X279" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="280">
-          <cell r="V280" t="str">
-            <v/>
-          </cell>
-          <cell r="W280" t="str">
-            <v/>
-          </cell>
-          <cell r="X280" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="281">
-          <cell r="V281" t="str">
-            <v/>
-          </cell>
-          <cell r="W281" t="str">
-            <v/>
-          </cell>
-          <cell r="X281" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="282">
-          <cell r="V282" t="str">
-            <v/>
-          </cell>
-          <cell r="W282" t="str">
-            <v/>
-          </cell>
-          <cell r="X282" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="283">
-          <cell r="V283" t="str">
-            <v/>
-          </cell>
-          <cell r="W283" t="str">
-            <v/>
-          </cell>
-          <cell r="X283" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="284">
-          <cell r="V284" t="str">
-            <v/>
-          </cell>
-          <cell r="W284" t="str">
-            <v/>
-          </cell>
-          <cell r="X284" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="285">
-          <cell r="V285" t="str">
-            <v/>
-          </cell>
-          <cell r="W285" t="str">
-            <v/>
-          </cell>
-          <cell r="X285" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="286">
-          <cell r="V286" t="str">
-            <v/>
-          </cell>
-          <cell r="W286" t="str">
-            <v/>
-          </cell>
-          <cell r="X286" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="287">
-          <cell r="V287" t="str">
-            <v/>
-          </cell>
-          <cell r="W287" t="str">
-            <v/>
-          </cell>
-          <cell r="X287" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="288">
-          <cell r="V288" t="str">
-            <v/>
-          </cell>
-          <cell r="W288" t="str">
-            <v/>
-          </cell>
-          <cell r="X288" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="289">
-          <cell r="V289" t="str">
-            <v/>
-          </cell>
-          <cell r="W289" t="str">
-            <v/>
-          </cell>
-          <cell r="X289" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="290">
-          <cell r="V290" t="str">
-            <v/>
-          </cell>
-          <cell r="W290" t="str">
-            <v/>
-          </cell>
-          <cell r="X290" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="291">
-          <cell r="V291" t="str">
-            <v/>
-          </cell>
-          <cell r="W291" t="str">
-            <v/>
-          </cell>
-          <cell r="X291" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="292">
-          <cell r="V292" t="str">
-            <v/>
-          </cell>
-          <cell r="W292" t="str">
-            <v/>
-          </cell>
-          <cell r="X292" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="293">
-          <cell r="V293" t="str">
-            <v/>
-          </cell>
-          <cell r="W293" t="str">
-            <v/>
-          </cell>
-          <cell r="X293" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="294">
-          <cell r="V294" t="str">
-            <v/>
-          </cell>
-          <cell r="W294" t="str">
-            <v/>
-          </cell>
-          <cell r="X294" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="295">
-          <cell r="V295" t="str">
-            <v/>
-          </cell>
-          <cell r="W295" t="str">
-            <v/>
-          </cell>
-          <cell r="X295" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="296">
-          <cell r="V296" t="str">
-            <v/>
-          </cell>
-          <cell r="W296" t="str">
-            <v/>
-          </cell>
-          <cell r="X296" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="297">
-          <cell r="V297" t="str">
-            <v/>
-          </cell>
-          <cell r="W297" t="str">
-            <v/>
-          </cell>
-          <cell r="X297" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="298">
-          <cell r="V298" t="str">
-            <v/>
-          </cell>
-          <cell r="W298" t="str">
-            <v/>
-          </cell>
-          <cell r="X298" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="299">
-          <cell r="V299" t="str">
-            <v/>
-          </cell>
-          <cell r="W299" t="str">
-            <v/>
-          </cell>
-          <cell r="X299" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="300">
-          <cell r="V300" t="str">
-            <v/>
-          </cell>
-          <cell r="W300" t="str">
-            <v/>
-          </cell>
-          <cell r="X300" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="301">
-          <cell r="V301" t="str">
-            <v/>
-          </cell>
-          <cell r="W301" t="str">
-            <v/>
-          </cell>
-          <cell r="X301" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="302">
-          <cell r="V302" t="str">
-            <v/>
-          </cell>
-          <cell r="W302" t="str">
-            <v/>
-          </cell>
-          <cell r="X302" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="303">
-          <cell r="V303" t="str">
-            <v/>
-          </cell>
-          <cell r="W303" t="str">
-            <v/>
-          </cell>
-          <cell r="X303" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="304">
-          <cell r="V304" t="str">
-            <v/>
-          </cell>
-          <cell r="W304" t="str">
-            <v/>
-          </cell>
-          <cell r="X304" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="305">
-          <cell r="V305" t="str">
-            <v/>
-          </cell>
-          <cell r="W305" t="str">
-            <v/>
-          </cell>
-          <cell r="X305" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="306">
-          <cell r="V306" t="str">
-            <v/>
-          </cell>
-          <cell r="W306" t="str">
-            <v/>
-          </cell>
-          <cell r="X306" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="307">
-          <cell r="V307" t="str">
-            <v/>
-          </cell>
-          <cell r="W307" t="str">
-            <v/>
-          </cell>
-          <cell r="X307" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="308">
-          <cell r="V308" t="str">
-            <v/>
-          </cell>
-          <cell r="W308" t="str">
-            <v/>
-          </cell>
-          <cell r="X308" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="309">
-          <cell r="V309" t="str">
-            <v/>
-          </cell>
-          <cell r="W309" t="str">
-            <v/>
-          </cell>
-          <cell r="X309" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="310">
-          <cell r="V310" t="str">
-            <v/>
-          </cell>
-          <cell r="W310" t="str">
-            <v/>
-          </cell>
-          <cell r="X310" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="311">
-          <cell r="V311" t="str">
-            <v/>
-          </cell>
-          <cell r="W311" t="str">
-            <v/>
-          </cell>
-          <cell r="X311" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="312">
-          <cell r="V312" t="str">
-            <v/>
-          </cell>
-          <cell r="W312" t="str">
-            <v/>
-          </cell>
-          <cell r="X312" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="313">
-          <cell r="V313" t="str">
-            <v/>
-          </cell>
-          <cell r="W313" t="str">
-            <v/>
-          </cell>
-          <cell r="X313" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="314">
-          <cell r="V314" t="str">
-            <v/>
-          </cell>
-          <cell r="W314" t="str">
-            <v/>
-          </cell>
-          <cell r="X314" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="315">
-          <cell r="V315" t="str">
-            <v/>
-          </cell>
-          <cell r="W315" t="str">
-            <v/>
-          </cell>
-          <cell r="X315" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="316">
-          <cell r="V316" t="str">
-            <v/>
-          </cell>
-          <cell r="W316" t="str">
-            <v/>
-          </cell>
-          <cell r="X316" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="317">
-          <cell r="V317" t="str">
-            <v/>
-          </cell>
-          <cell r="W317" t="str">
-            <v/>
-          </cell>
-          <cell r="X317" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="318">
-          <cell r="V318" t="str">
-            <v/>
-          </cell>
-          <cell r="W318" t="str">
-            <v/>
-          </cell>
-          <cell r="X318" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="319">
-          <cell r="V319" t="str">
-            <v/>
-          </cell>
-          <cell r="W319" t="str">
-            <v/>
-          </cell>
-          <cell r="X319" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="320">
-          <cell r="V320" t="str">
-            <v/>
-          </cell>
-          <cell r="W320" t="str">
-            <v/>
-          </cell>
-          <cell r="X320" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="321">
-          <cell r="V321" t="str">
-            <v/>
-          </cell>
-          <cell r="W321" t="str">
-            <v/>
-          </cell>
-          <cell r="X321" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="322">
-          <cell r="V322" t="str">
-            <v/>
-          </cell>
-          <cell r="W322" t="str">
-            <v/>
-          </cell>
-          <cell r="X322" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="323">
-          <cell r="V323" t="str">
-            <v/>
-          </cell>
-          <cell r="W323" t="str">
-            <v/>
-          </cell>
-          <cell r="X323" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="324">
-          <cell r="V324" t="str">
-            <v/>
-          </cell>
-          <cell r="W324" t="str">
-            <v/>
-          </cell>
-          <cell r="X324" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="325">
-          <cell r="V325" t="str">
-            <v/>
-          </cell>
-          <cell r="W325" t="str">
-            <v/>
-          </cell>
-          <cell r="X325" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="326">
-          <cell r="V326" t="str">
-            <v/>
-          </cell>
-          <cell r="W326" t="str">
-            <v/>
-          </cell>
-          <cell r="X326" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="327">
-          <cell r="V327" t="str">
-            <v/>
-          </cell>
-          <cell r="W327" t="str">
-            <v/>
-          </cell>
-          <cell r="X327" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="328">
-          <cell r="V328" t="str">
-            <v/>
-          </cell>
-          <cell r="W328" t="str">
-            <v/>
-          </cell>
-          <cell r="X328" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="329">
-          <cell r="V329" t="str">
-            <v/>
-          </cell>
-          <cell r="W329" t="str">
-            <v/>
-          </cell>
-          <cell r="X329" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="330">
-          <cell r="V330" t="str">
-            <v/>
-          </cell>
-          <cell r="W330" t="str">
-            <v/>
-          </cell>
-          <cell r="X330" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="331">
-          <cell r="V331" t="str">
-            <v/>
-          </cell>
-          <cell r="W331" t="str">
-            <v/>
-          </cell>
-          <cell r="X331" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="332">
-          <cell r="V332" t="str">
-            <v/>
-          </cell>
-          <cell r="W332" t="str">
-            <v/>
-          </cell>
-          <cell r="X332" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="333">
-          <cell r="V333" t="str">
-            <v/>
-          </cell>
-          <cell r="W333" t="str">
-            <v/>
-          </cell>
-          <cell r="X333" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="334">
-          <cell r="V334" t="str">
-            <v/>
-          </cell>
-          <cell r="W334" t="str">
-            <v/>
-          </cell>
-          <cell r="X334" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="335">
-          <cell r="V335" t="str">
-            <v/>
-          </cell>
-          <cell r="W335" t="str">
-            <v/>
-          </cell>
-          <cell r="X335" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="336">
-          <cell r="V336" t="str">
-            <v/>
-          </cell>
-          <cell r="W336" t="str">
-            <v/>
-          </cell>
-          <cell r="X336" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="337">
-          <cell r="V337" t="str">
-            <v/>
-          </cell>
-          <cell r="W337" t="str">
-            <v/>
-          </cell>
-          <cell r="X337" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="338">
-          <cell r="V338" t="str">
-            <v/>
-          </cell>
-          <cell r="W338" t="str">
-            <v/>
-          </cell>
-          <cell r="X338" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="339">
-          <cell r="V339" t="str">
-            <v/>
-          </cell>
-          <cell r="W339" t="str">
-            <v/>
-          </cell>
-          <cell r="X339" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="340">
-          <cell r="V340" t="str">
-            <v/>
-          </cell>
-          <cell r="W340" t="str">
-            <v/>
-          </cell>
-          <cell r="X340" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="341">
-          <cell r="V341" t="str">
-            <v/>
-          </cell>
-          <cell r="W341" t="str">
-            <v/>
-          </cell>
-          <cell r="X341" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="342">
-          <cell r="V342" t="str">
-            <v/>
-          </cell>
-          <cell r="W342" t="str">
-            <v/>
-          </cell>
-          <cell r="X342" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="343">
-          <cell r="V343" t="str">
-            <v/>
-          </cell>
-          <cell r="W343" t="str">
-            <v/>
-          </cell>
-          <cell r="X343" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="344">
-          <cell r="V344" t="str">
-            <v/>
-          </cell>
-          <cell r="W344" t="str">
-            <v/>
-          </cell>
-          <cell r="X344" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="345">
-          <cell r="V345" t="str">
-            <v/>
-          </cell>
-          <cell r="W345" t="str">
-            <v/>
-          </cell>
-          <cell r="X345" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="346">
-          <cell r="V346" t="str">
-            <v/>
-          </cell>
-          <cell r="W346" t="str">
-            <v/>
-          </cell>
-          <cell r="X346" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="347">
-          <cell r="V347" t="str">
-            <v/>
-          </cell>
-          <cell r="W347" t="str">
-            <v/>
-          </cell>
-          <cell r="X347" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="348">
-          <cell r="V348" t="str">
-            <v/>
-          </cell>
-          <cell r="W348" t="str">
-            <v/>
-          </cell>
-          <cell r="X348" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="349">
-          <cell r="V349" t="str">
-            <v/>
-          </cell>
-          <cell r="W349" t="str">
-            <v/>
-          </cell>
-          <cell r="X349" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="350">
-          <cell r="V350" t="str">
-            <v/>
-          </cell>
-          <cell r="W350" t="str">
-            <v/>
-          </cell>
-          <cell r="X350" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="351">
-          <cell r="V351" t="str">
-            <v/>
-          </cell>
-          <cell r="W351" t="str">
-            <v/>
-          </cell>
-          <cell r="X351" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="352">
-          <cell r="V352" t="str">
-            <v/>
-          </cell>
-          <cell r="W352" t="str">
-            <v/>
-          </cell>
-          <cell r="X352" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="353">
-          <cell r="V353" t="str">
-            <v/>
-          </cell>
-          <cell r="W353" t="str">
-            <v/>
-          </cell>
-          <cell r="X353" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="354">
-          <cell r="V354" t="str">
-            <v/>
-          </cell>
-          <cell r="W354" t="str">
-            <v/>
-          </cell>
-          <cell r="X354" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="355">
-          <cell r="V355" t="str">
-            <v/>
-          </cell>
-          <cell r="W355" t="str">
-            <v/>
-          </cell>
-          <cell r="X355" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="356">
-          <cell r="V356" t="str">
-            <v/>
-          </cell>
-          <cell r="W356" t="str">
-            <v/>
-          </cell>
-          <cell r="X356" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="357">
-          <cell r="V357" t="str">
-            <v/>
-          </cell>
-          <cell r="W357" t="str">
-            <v/>
-          </cell>
-          <cell r="X357" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="358">
-          <cell r="V358" t="str">
-            <v/>
-          </cell>
-          <cell r="W358" t="str">
-            <v/>
-          </cell>
-          <cell r="X358" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="359">
-          <cell r="V359" t="str">
-            <v/>
-          </cell>
-          <cell r="W359" t="str">
-            <v/>
-          </cell>
-          <cell r="X359" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="360">
-          <cell r="V360" t="str">
-            <v/>
-          </cell>
-          <cell r="W360" t="str">
-            <v/>
-          </cell>
-          <cell r="X360" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="361">
-          <cell r="V361" t="str">
-            <v/>
-          </cell>
-          <cell r="W361" t="str">
-            <v/>
-          </cell>
-          <cell r="X361" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="362">
-          <cell r="V362" t="str">
-            <v/>
-          </cell>
-          <cell r="W362" t="str">
-            <v/>
-          </cell>
-          <cell r="X362" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="363">
-          <cell r="V363" t="str">
-            <v/>
-          </cell>
-          <cell r="W363" t="str">
-            <v/>
-          </cell>
-          <cell r="X363" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="364">
-          <cell r="V364" t="str">
-            <v/>
-          </cell>
-          <cell r="W364" t="str">
-            <v/>
-          </cell>
-          <cell r="X364" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="365">
-          <cell r="V365" t="str">
-            <v/>
-          </cell>
-          <cell r="W365" t="str">
-            <v/>
-          </cell>
-          <cell r="X365" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="366">
-          <cell r="V366" t="str">
-            <v/>
-          </cell>
-          <cell r="W366" t="str">
-            <v/>
-          </cell>
-          <cell r="X366" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="367">
-          <cell r="V367" t="str">
-            <v/>
-          </cell>
-          <cell r="W367" t="str">
-            <v/>
-          </cell>
-          <cell r="X367" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="368">
-          <cell r="V368" t="str">
-            <v/>
-          </cell>
-          <cell r="W368" t="str">
-            <v/>
-          </cell>
-          <cell r="X368" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="369">
-          <cell r="V369" t="str">
-            <v/>
-          </cell>
-          <cell r="W369" t="str">
-            <v/>
-          </cell>
-          <cell r="X369" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="370">
-          <cell r="V370" t="str">
-            <v/>
-          </cell>
-          <cell r="W370" t="str">
-            <v/>
-          </cell>
-          <cell r="X370" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="371">
-          <cell r="V371" t="str">
-            <v/>
-          </cell>
-          <cell r="W371" t="str">
-            <v/>
-          </cell>
-          <cell r="X371" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="372">
-          <cell r="V372" t="str">
-            <v/>
-          </cell>
-          <cell r="W372" t="str">
-            <v/>
-          </cell>
-          <cell r="X372" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="373">
-          <cell r="V373" t="str">
-            <v/>
-          </cell>
-          <cell r="W373" t="str">
-            <v/>
-          </cell>
-          <cell r="X373" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="374">
-          <cell r="V374" t="str">
-            <v/>
-          </cell>
-          <cell r="W374" t="str">
-            <v/>
-          </cell>
-          <cell r="X374" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="375">
-          <cell r="V375" t="str">
-            <v/>
-          </cell>
-          <cell r="W375" t="str">
-            <v/>
-          </cell>
-          <cell r="X375" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="376">
-          <cell r="V376" t="str">
-            <v/>
-          </cell>
-          <cell r="W376" t="str">
-            <v/>
-          </cell>
-          <cell r="X376" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="377">
-          <cell r="V377" t="str">
-            <v/>
-          </cell>
-          <cell r="W377" t="str">
-            <v/>
-          </cell>
-          <cell r="X377" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="378">
-          <cell r="V378" t="str">
-            <v/>
-          </cell>
-          <cell r="W378" t="str">
-            <v/>
-          </cell>
-          <cell r="X378" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="379">
-          <cell r="V379" t="str">
-            <v/>
-          </cell>
-          <cell r="W379" t="str">
-            <v/>
-          </cell>
-          <cell r="X379" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="380">
-          <cell r="V380" t="str">
-            <v/>
-          </cell>
-          <cell r="W380" t="str">
-            <v/>
-          </cell>
-          <cell r="X380" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="381">
-          <cell r="V381" t="str">
-            <v/>
-          </cell>
-          <cell r="W381" t="str">
-            <v/>
-          </cell>
-          <cell r="X381" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="382">
-          <cell r="V382" t="str">
-            <v/>
-          </cell>
-          <cell r="W382" t="str">
-            <v/>
-          </cell>
-          <cell r="X382" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="383">
-          <cell r="V383" t="str">
-            <v/>
-          </cell>
-          <cell r="W383" t="str">
-            <v/>
-          </cell>
-          <cell r="X383" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="384">
-          <cell r="V384" t="str">
-            <v/>
-          </cell>
-          <cell r="W384" t="str">
-            <v/>
-          </cell>
-          <cell r="X384" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="385">
-          <cell r="V385" t="str">
-            <v/>
-          </cell>
-          <cell r="W385" t="str">
-            <v/>
-          </cell>
-          <cell r="X385" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="386">
-          <cell r="V386" t="str">
-            <v/>
-          </cell>
-          <cell r="W386" t="str">
-            <v/>
-          </cell>
-          <cell r="X386" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="387">
-          <cell r="V387" t="str">
-            <v/>
-          </cell>
-          <cell r="W387" t="str">
-            <v/>
-          </cell>
-          <cell r="X387" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="388">
-          <cell r="V388" t="str">
-            <v/>
-          </cell>
-          <cell r="W388" t="str">
-            <v/>
-          </cell>
-          <cell r="X388" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="389">
-          <cell r="V389" t="str">
-            <v/>
-          </cell>
-          <cell r="W389" t="str">
-            <v/>
-          </cell>
-          <cell r="X389" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="390">
-          <cell r="V390" t="str">
-            <v/>
-          </cell>
-          <cell r="W390" t="str">
-            <v/>
-          </cell>
-          <cell r="X390" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="391">
-          <cell r="V391" t="str">
-            <v/>
-          </cell>
-          <cell r="W391" t="str">
-            <v/>
-          </cell>
-          <cell r="X391" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="392">
-          <cell r="V392" t="str">
-            <v/>
-          </cell>
-          <cell r="W392" t="str">
-            <v/>
-          </cell>
-          <cell r="X392" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="393">
-          <cell r="V393" t="str">
-            <v/>
-          </cell>
-          <cell r="W393" t="str">
-            <v/>
-          </cell>
-          <cell r="X393" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="394">
-          <cell r="V394" t="str">
-            <v/>
-          </cell>
-          <cell r="W394" t="str">
-            <v/>
-          </cell>
-          <cell r="X394" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="395">
-          <cell r="V395" t="str">
-            <v/>
-          </cell>
-          <cell r="W395" t="str">
-            <v/>
-          </cell>
-          <cell r="X395" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="396">
-          <cell r="V396" t="str">
-            <v/>
-          </cell>
-          <cell r="W396" t="str">
-            <v/>
-          </cell>
-          <cell r="X396" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="397">
-          <cell r="V397" t="str">
-            <v/>
-          </cell>
-          <cell r="W397" t="str">
-            <v/>
-          </cell>
-          <cell r="X397" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="398">
-          <cell r="V398" t="str">
-            <v/>
-          </cell>
-          <cell r="W398" t="str">
-            <v/>
-          </cell>
-          <cell r="X398" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="399">
-          <cell r="V399" t="str">
-            <v/>
-          </cell>
-          <cell r="W399" t="str">
-            <v/>
-          </cell>
-          <cell r="X399" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="400">
-          <cell r="V400" t="str">
-            <v/>
-          </cell>
-          <cell r="W400" t="str">
-            <v/>
-          </cell>
-          <cell r="X400" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="401">
-          <cell r="V401" t="str">
-            <v/>
-          </cell>
-          <cell r="W401" t="str">
-            <v/>
-          </cell>
-          <cell r="X401" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="402">
-          <cell r="V402" t="str">
-            <v/>
-          </cell>
-          <cell r="W402" t="str">
-            <v/>
-          </cell>
-          <cell r="X402" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="403">
-          <cell r="V403" t="str">
-            <v/>
-          </cell>
-          <cell r="W403" t="str">
-            <v/>
-          </cell>
-          <cell r="X403" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="404">
-          <cell r="V404" t="str">
-            <v/>
-          </cell>
-          <cell r="W404" t="str">
-            <v/>
-          </cell>
-          <cell r="X404" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="405">
-          <cell r="V405" t="str">
-            <v/>
-          </cell>
-          <cell r="W405" t="str">
-            <v/>
-          </cell>
-          <cell r="X405" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="406">
-          <cell r="V406" t="str">
-            <v/>
-          </cell>
-          <cell r="W406" t="str">
-            <v/>
-          </cell>
-          <cell r="X406" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="407">
-          <cell r="V407" t="str">
-            <v/>
-          </cell>
-          <cell r="W407" t="str">
-            <v/>
-          </cell>
-          <cell r="X407" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="408">
-          <cell r="V408" t="str">
-            <v/>
-          </cell>
-          <cell r="W408" t="str">
-            <v/>
-          </cell>
-          <cell r="X408" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="409">
-          <cell r="V409" t="str">
-            <v/>
-          </cell>
-          <cell r="W409" t="str">
-            <v/>
-          </cell>
-          <cell r="X409" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="410">
-          <cell r="V410" t="str">
-            <v/>
-          </cell>
-          <cell r="W410" t="str">
-            <v/>
-          </cell>
-          <cell r="X410" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="411">
-          <cell r="V411" t="str">
-            <v/>
-          </cell>
-          <cell r="W411" t="str">
-            <v/>
-          </cell>
-          <cell r="X411" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="412">
-          <cell r="V412" t="str">
-            <v/>
-          </cell>
-          <cell r="W412" t="str">
-            <v/>
-          </cell>
-          <cell r="X412" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="413">
-          <cell r="V413" t="str">
-            <v/>
-          </cell>
-          <cell r="W413" t="str">
-            <v/>
-          </cell>
-          <cell r="X413" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="414">
-          <cell r="V414" t="str">
-            <v/>
-          </cell>
-          <cell r="W414" t="str">
-            <v/>
-          </cell>
-          <cell r="X414" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="415">
-          <cell r="V415" t="str">
-            <v/>
-          </cell>
-          <cell r="W415" t="str">
-            <v/>
-          </cell>
-          <cell r="X415" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="416">
-          <cell r="V416" t="str">
-            <v/>
-          </cell>
-          <cell r="W416" t="str">
-            <v/>
-          </cell>
-          <cell r="X416" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="417">
-          <cell r="V417" t="str">
-            <v/>
-          </cell>
-          <cell r="W417" t="str">
-            <v/>
-          </cell>
-          <cell r="X417" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="418">
-          <cell r="V418" t="str">
-            <v/>
-          </cell>
-          <cell r="W418" t="str">
-            <v/>
-          </cell>
-          <cell r="X418" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="419">
-          <cell r="V419" t="str">
-            <v/>
-          </cell>
-          <cell r="W419" t="str">
-            <v/>
-          </cell>
-          <cell r="X419" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="420">
-          <cell r="V420" t="str">
-            <v/>
-          </cell>
-          <cell r="W420" t="str">
-            <v/>
-          </cell>
-          <cell r="X420" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="421">
-          <cell r="V421" t="str">
-            <v/>
-          </cell>
-          <cell r="W421" t="str">
-            <v/>
-          </cell>
-          <cell r="X421" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="422">
-          <cell r="V422" t="str">
-            <v/>
-          </cell>
-          <cell r="W422" t="str">
-            <v/>
-          </cell>
-          <cell r="X422" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="423">
-          <cell r="V423" t="str">
-            <v/>
-          </cell>
-          <cell r="W423" t="str">
-            <v/>
-          </cell>
-          <cell r="X423" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="424">
-          <cell r="V424" t="str">
-            <v/>
-          </cell>
-          <cell r="W424" t="str">
-            <v/>
-          </cell>
-          <cell r="X424" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="425">
-          <cell r="V425" t="str">
-            <v/>
-          </cell>
-          <cell r="W425" t="str">
-            <v/>
-          </cell>
-          <cell r="X425" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="426">
-          <cell r="V426" t="str">
-            <v/>
-          </cell>
-          <cell r="W426" t="str">
-            <v/>
-          </cell>
-          <cell r="X426" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="427">
-          <cell r="V427" t="str">
-            <v/>
-          </cell>
-          <cell r="W427" t="str">
-            <v/>
-          </cell>
-          <cell r="X427" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="428">
-          <cell r="V428" t="str">
-            <v/>
-          </cell>
-          <cell r="W428" t="str">
-            <v/>
-          </cell>
-          <cell r="X428" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="429">
-          <cell r="V429" t="str">
-            <v/>
-          </cell>
-          <cell r="W429" t="str">
-            <v/>
-          </cell>
-          <cell r="X429" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="430">
-          <cell r="V430" t="str">
-            <v/>
-          </cell>
-          <cell r="W430" t="str">
-            <v/>
-          </cell>
-          <cell r="X430" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="431">
-          <cell r="V431" t="str">
-            <v/>
-          </cell>
-          <cell r="W431" t="str">
-            <v/>
-          </cell>
-          <cell r="X431" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="432">
-          <cell r="V432" t="str">
-            <v/>
-          </cell>
-          <cell r="W432" t="str">
-            <v/>
-          </cell>
-          <cell r="X432" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="433">
-          <cell r="V433" t="str">
-            <v/>
-          </cell>
-          <cell r="W433" t="str">
-            <v/>
-          </cell>
-          <cell r="X433" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="434">
-          <cell r="V434" t="str">
-            <v/>
-          </cell>
-          <cell r="W434" t="str">
-            <v/>
-          </cell>
-          <cell r="X434" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="435">
-          <cell r="V435" t="str">
-            <v/>
-          </cell>
-          <cell r="W435" t="str">
-            <v/>
-          </cell>
-          <cell r="X435" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="436">
-          <cell r="V436" t="str">
-            <v/>
-          </cell>
-          <cell r="W436" t="str">
-            <v/>
-          </cell>
-          <cell r="X436" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="437">
-          <cell r="V437" t="str">
-            <v/>
-          </cell>
-          <cell r="W437" t="str">
-            <v/>
-          </cell>
-          <cell r="X437" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="438">
-          <cell r="V438" t="str">
-            <v/>
-          </cell>
-          <cell r="W438" t="str">
-            <v/>
-          </cell>
-          <cell r="X438" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="439">
-          <cell r="V439" t="str">
-            <v/>
-          </cell>
-          <cell r="W439" t="str">
-            <v/>
-          </cell>
-          <cell r="X439" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="440">
-          <cell r="V440" t="str">
-            <v/>
-          </cell>
-          <cell r="W440" t="str">
-            <v/>
-          </cell>
-          <cell r="X440" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="441">
-          <cell r="V441" t="str">
-            <v/>
-          </cell>
-          <cell r="W441" t="str">
-            <v/>
-          </cell>
-          <cell r="X441" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="442">
-          <cell r="V442" t="str">
-            <v/>
-          </cell>
-          <cell r="W442" t="str">
-            <v/>
-          </cell>
-          <cell r="X442" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="443">
-          <cell r="V443" t="str">
-            <v/>
-          </cell>
-          <cell r="W443" t="str">
-            <v/>
-          </cell>
-          <cell r="X443" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="444">
-          <cell r="V444" t="str">
-            <v/>
-          </cell>
-          <cell r="W444" t="str">
-            <v/>
-          </cell>
-          <cell r="X444" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="445">
-          <cell r="V445" t="str">
-            <v/>
-          </cell>
-          <cell r="W445" t="str">
-            <v/>
-          </cell>
-          <cell r="X445" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="446">
-          <cell r="V446" t="str">
-            <v/>
-          </cell>
-          <cell r="W446" t="str">
-            <v/>
-          </cell>
-          <cell r="X446" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="447">
-          <cell r="V447" t="str">
-            <v/>
-          </cell>
-          <cell r="W447" t="str">
-            <v/>
-          </cell>
-          <cell r="X447" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="448">
-          <cell r="V448" t="str">
-            <v/>
-          </cell>
-          <cell r="W448" t="str">
-            <v/>
-          </cell>
-          <cell r="X448" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="449">
-          <cell r="V449" t="str">
-            <v/>
-          </cell>
-          <cell r="W449" t="str">
-            <v/>
-          </cell>
-          <cell r="X449" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="450">
-          <cell r="V450" t="str">
-            <v/>
-          </cell>
-          <cell r="W450" t="str">
-            <v/>
-          </cell>
-          <cell r="X450" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="451">
-          <cell r="V451" t="str">
-            <v/>
-          </cell>
-          <cell r="W451" t="str">
-            <v/>
-          </cell>
-          <cell r="X451" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="452">
-          <cell r="V452" t="str">
-            <v/>
-          </cell>
-          <cell r="W452" t="str">
-            <v/>
-          </cell>
-          <cell r="X452" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="453">
-          <cell r="V453" t="str">
-            <v/>
-          </cell>
-          <cell r="W453" t="str">
-            <v/>
-          </cell>
-          <cell r="X453" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="454">
-          <cell r="V454" t="str">
-            <v/>
-          </cell>
-          <cell r="W454" t="str">
-            <v/>
-          </cell>
-          <cell r="X454" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="455">
-          <cell r="V455" t="str">
-            <v/>
-          </cell>
-          <cell r="W455" t="str">
-            <v/>
-          </cell>
-          <cell r="X455" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="456">
-          <cell r="V456" t="str">
-            <v/>
-          </cell>
-          <cell r="W456" t="str">
-            <v/>
-          </cell>
-          <cell r="X456" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="457">
-          <cell r="V457" t="str">
-            <v/>
-          </cell>
-          <cell r="W457" t="str">
-            <v/>
-          </cell>
-          <cell r="X457" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="458">
-          <cell r="V458" t="str">
-            <v/>
-          </cell>
-          <cell r="W458" t="str">
-            <v/>
-          </cell>
-          <cell r="X458" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="459">
-          <cell r="V459" t="str">
-            <v/>
-          </cell>
-          <cell r="W459" t="str">
-            <v/>
-          </cell>
-          <cell r="X459" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="460">
-          <cell r="V460" t="str">
-            <v/>
-          </cell>
-          <cell r="W460" t="str">
-            <v/>
-          </cell>
-          <cell r="X460" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="461">
-          <cell r="V461" t="str">
-            <v/>
-          </cell>
-          <cell r="W461" t="str">
-            <v/>
-          </cell>
-          <cell r="X461" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="462">
-          <cell r="V462" t="str">
-            <v/>
-          </cell>
-          <cell r="W462" t="str">
-            <v/>
-          </cell>
-          <cell r="X462" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="463">
-          <cell r="V463" t="str">
-            <v/>
-          </cell>
-          <cell r="W463" t="str">
-            <v/>
-          </cell>
-          <cell r="X463" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="464">
-          <cell r="V464" t="str">
-            <v/>
-          </cell>
-          <cell r="W464" t="str">
-            <v/>
-          </cell>
-          <cell r="X464" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="465">
-          <cell r="V465" t="str">
-            <v/>
-          </cell>
-          <cell r="W465" t="str">
-            <v/>
-          </cell>
-          <cell r="X465" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="466">
-          <cell r="V466" t="str">
-            <v/>
-          </cell>
-          <cell r="W466" t="str">
-            <v/>
-          </cell>
-          <cell r="X466" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="467">
-          <cell r="V467" t="str">
-            <v/>
-          </cell>
-          <cell r="W467" t="str">
-            <v/>
-          </cell>
-          <cell r="X467" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="468">
-          <cell r="V468" t="str">
-            <v/>
-          </cell>
-          <cell r="W468" t="str">
-            <v/>
-          </cell>
-          <cell r="X468" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="469">
-          <cell r="V469" t="str">
-            <v/>
-          </cell>
-          <cell r="W469" t="str">
-            <v/>
-          </cell>
-          <cell r="X469" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="470">
-          <cell r="V470" t="str">
-            <v/>
-          </cell>
-          <cell r="W470" t="str">
-            <v/>
-          </cell>
-          <cell r="X470" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="471">
-          <cell r="V471" t="str">
-            <v/>
-          </cell>
-          <cell r="W471" t="str">
-            <v/>
-          </cell>
-          <cell r="X471" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="472">
-          <cell r="V472" t="str">
-            <v/>
-          </cell>
-          <cell r="W472" t="str">
-            <v/>
-          </cell>
-          <cell r="X472" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="473">
-          <cell r="V473" t="str">
-            <v/>
-          </cell>
-          <cell r="W473" t="str">
-            <v/>
-          </cell>
-          <cell r="X473" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="474">
-          <cell r="V474" t="str">
-            <v/>
-          </cell>
-          <cell r="W474" t="str">
-            <v/>
-          </cell>
-          <cell r="X474" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="475">
-          <cell r="V475" t="str">
-            <v/>
-          </cell>
-          <cell r="W475" t="str">
-            <v/>
-          </cell>
-          <cell r="X475" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="476">
-          <cell r="V476" t="str">
-            <v/>
-          </cell>
-          <cell r="W476" t="str">
-            <v/>
-          </cell>
-          <cell r="X476" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="477">
-          <cell r="V477" t="str">
-            <v/>
-          </cell>
-          <cell r="W477" t="str">
-            <v/>
-          </cell>
-          <cell r="X477" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="478">
-          <cell r="V478" t="str">
-            <v/>
-          </cell>
-          <cell r="W478" t="str">
-            <v/>
-          </cell>
-          <cell r="X478" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="479">
-          <cell r="V479" t="str">
-            <v/>
-          </cell>
-          <cell r="W479" t="str">
-            <v/>
-          </cell>
-          <cell r="X479" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="480">
-          <cell r="V480" t="str">
-            <v/>
-          </cell>
-          <cell r="W480" t="str">
-            <v/>
-          </cell>
-          <cell r="X480" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="481">
-          <cell r="V481" t="str">
-            <v/>
-          </cell>
-          <cell r="W481" t="str">
-            <v/>
-          </cell>
-          <cell r="X481" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="482">
-          <cell r="V482" t="str">
-            <v/>
-          </cell>
-          <cell r="W482" t="str">
-            <v/>
-          </cell>
-          <cell r="X482" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="483">
-          <cell r="V483" t="str">
-            <v/>
-          </cell>
-          <cell r="W483" t="str">
-            <v/>
-          </cell>
-          <cell r="X483" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="484">
-          <cell r="V484" t="str">
-            <v/>
-          </cell>
-          <cell r="W484" t="str">
-            <v/>
-          </cell>
-          <cell r="X484" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="485">
-          <cell r="V485" t="str">
-            <v/>
-          </cell>
-          <cell r="W485" t="str">
-            <v/>
-          </cell>
-          <cell r="X485" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="486">
-          <cell r="V486" t="str">
-            <v/>
-          </cell>
-          <cell r="W486" t="str">
-            <v/>
-          </cell>
-          <cell r="X486" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="487">
-          <cell r="V487" t="str">
-            <v/>
-          </cell>
-          <cell r="W487" t="str">
-            <v/>
-          </cell>
-          <cell r="X487" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="488">
-          <cell r="V488" t="str">
-            <v/>
-          </cell>
-          <cell r="W488" t="str">
-            <v/>
-          </cell>
-          <cell r="X488" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="489">
-          <cell r="V489" t="str">
-            <v/>
-          </cell>
-          <cell r="W489" t="str">
-            <v/>
-          </cell>
-          <cell r="X489" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="490">
-          <cell r="V490" t="str">
-            <v/>
-          </cell>
-          <cell r="W490" t="str">
-            <v/>
-          </cell>
-          <cell r="X490" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="491">
-          <cell r="V491" t="str">
-            <v/>
-          </cell>
-          <cell r="W491" t="str">
-            <v/>
-          </cell>
-          <cell r="X491" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="492">
-          <cell r="V492" t="str">
-            <v/>
-          </cell>
-          <cell r="W492" t="str">
-            <v/>
-          </cell>
-          <cell r="X492" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="493">
-          <cell r="V493" t="str">
-            <v/>
-          </cell>
-          <cell r="W493" t="str">
-            <v/>
-          </cell>
-          <cell r="X493" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="494">
-          <cell r="V494" t="str">
-            <v/>
-          </cell>
-          <cell r="W494" t="str">
-            <v/>
-          </cell>
-          <cell r="X494" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="495">
-          <cell r="V495" t="str">
-            <v/>
-          </cell>
-          <cell r="W495" t="str">
-            <v/>
-          </cell>
-          <cell r="X495" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="496">
-          <cell r="V496" t="str">
-            <v/>
-          </cell>
-          <cell r="W496" t="str">
-            <v/>
-          </cell>
-          <cell r="X496" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="497">
-          <cell r="V497" t="str">
-            <v/>
-          </cell>
-          <cell r="W497" t="str">
-            <v/>
-          </cell>
-          <cell r="X497" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="498">
-          <cell r="V498" t="str">
-            <v/>
-          </cell>
-          <cell r="W498" t="str">
-            <v/>
-          </cell>
-          <cell r="X498" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="499">
-          <cell r="V499" t="str">
-            <v/>
-          </cell>
-          <cell r="W499" t="str">
-            <v/>
-          </cell>
-          <cell r="X499" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="500">
-          <cell r="V500" t="str">
-            <v/>
-          </cell>
-          <cell r="W500" t="str">
-            <v/>
-          </cell>
-          <cell r="X500" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="501">
-          <cell r="V501" t="str">
-            <v/>
-          </cell>
-          <cell r="W501" t="str">
-            <v/>
-          </cell>
-          <cell r="X501" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="502">
-          <cell r="V502" t="str">
-            <v/>
-          </cell>
-          <cell r="W502" t="str">
-            <v/>
-          </cell>
-          <cell r="X502" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="503">
-          <cell r="V503" t="str">
-            <v/>
-          </cell>
-          <cell r="W503" t="str">
-            <v/>
-          </cell>
-          <cell r="X503" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="504">
-          <cell r="V504" t="str">
-            <v/>
-          </cell>
-          <cell r="W504" t="str">
-            <v/>
-          </cell>
-          <cell r="X504" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="505">
-          <cell r="V505" t="str">
-            <v/>
-          </cell>
-          <cell r="W505" t="str">
-            <v/>
-          </cell>
-          <cell r="X505" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="506">
-          <cell r="V506" t="str">
-            <v/>
-          </cell>
-          <cell r="W506" t="str">
-            <v/>
-          </cell>
-          <cell r="X506" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="507">
-          <cell r="V507" t="str">
-            <v/>
-          </cell>
-          <cell r="W507" t="str">
-            <v/>
-          </cell>
-          <cell r="X507" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="508">
-          <cell r="V508" t="str">
-            <v/>
-          </cell>
-          <cell r="W508" t="str">
-            <v/>
-          </cell>
-          <cell r="X508" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="509">
-          <cell r="V509" t="str">
-            <v/>
-          </cell>
-          <cell r="W509" t="str">
-            <v/>
-          </cell>
-          <cell r="X509" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="510">
-          <cell r="V510" t="str">
-            <v/>
-          </cell>
-          <cell r="W510" t="str">
-            <v/>
-          </cell>
-          <cell r="X510" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="511">
-          <cell r="V511" t="str">
-            <v/>
-          </cell>
-          <cell r="W511" t="str">
-            <v/>
-          </cell>
-          <cell r="X511" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="512">
-          <cell r="V512" t="str">
-            <v/>
-          </cell>
-          <cell r="W512" t="str">
-            <v/>
-          </cell>
-          <cell r="X512" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="513">
-          <cell r="V513" t="str">
-            <v/>
-          </cell>
-          <cell r="W513" t="str">
-            <v/>
-          </cell>
-          <cell r="X513" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="514">
-          <cell r="V514" t="str">
-            <v/>
-          </cell>
-          <cell r="W514" t="str">
-            <v/>
-          </cell>
-          <cell r="X514" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="515">
-          <cell r="V515" t="str">
-            <v/>
-          </cell>
-          <cell r="W515" t="str">
-            <v/>
-          </cell>
-          <cell r="X515" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="516">
-          <cell r="V516" t="str">
-            <v/>
-          </cell>
-          <cell r="W516" t="str">
-            <v/>
-          </cell>
-          <cell r="X516" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="517">
-          <cell r="V517" t="str">
-            <v/>
-          </cell>
-          <cell r="W517" t="str">
-            <v/>
-          </cell>
-          <cell r="X517" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="518">
-          <cell r="V518" t="str">
-            <v/>
-          </cell>
-          <cell r="W518" t="str">
-            <v/>
-          </cell>
-          <cell r="X518" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="519">
-          <cell r="V519" t="str">
-            <v/>
-          </cell>
-          <cell r="W519" t="str">
-            <v/>
-          </cell>
-          <cell r="X519" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="520">
-          <cell r="V520" t="str">
-            <v/>
-          </cell>
-          <cell r="W520" t="str">
-            <v/>
-          </cell>
-          <cell r="X520" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="521">
-          <cell r="V521" t="str">
-            <v/>
-          </cell>
-          <cell r="W521" t="str">
-            <v/>
-          </cell>
-          <cell r="X521" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="522">
-          <cell r="V522" t="str">
-            <v/>
-          </cell>
-          <cell r="W522" t="str">
-            <v/>
-          </cell>
-          <cell r="X522" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="523">
-          <cell r="V523" t="str">
-            <v/>
-          </cell>
-          <cell r="W523" t="str">
-            <v/>
-          </cell>
-          <cell r="X523" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="524">
-          <cell r="V524" t="str">
-            <v/>
-          </cell>
-          <cell r="W524" t="str">
-            <v/>
-          </cell>
-          <cell r="X524" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="525">
-          <cell r="V525" t="str">
-            <v/>
-          </cell>
-          <cell r="W525" t="str">
-            <v/>
-          </cell>
-          <cell r="X525" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="526">
-          <cell r="V526" t="str">
-            <v/>
-          </cell>
-          <cell r="W526" t="str">
-            <v/>
-          </cell>
-          <cell r="X526" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="527">
-          <cell r="V527" t="str">
-            <v/>
-          </cell>
-          <cell r="W527" t="str">
-            <v/>
-          </cell>
-          <cell r="X527" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="528">
-          <cell r="V528" t="str">
-            <v/>
-          </cell>
-          <cell r="W528" t="str">
-            <v/>
-          </cell>
-          <cell r="X528" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="529">
-          <cell r="V529" t="str">
-            <v/>
-          </cell>
-          <cell r="W529" t="str">
-            <v/>
-          </cell>
-          <cell r="X529" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="530">
-          <cell r="V530" t="str">
-            <v/>
-          </cell>
-          <cell r="W530" t="str">
-            <v/>
-          </cell>
-          <cell r="X530" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="531">
-          <cell r="V531" t="str">
-            <v/>
-          </cell>
-          <cell r="W531" t="str">
-            <v/>
-          </cell>
-          <cell r="X531" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="532">
-          <cell r="V532" t="str">
-            <v/>
-          </cell>
-          <cell r="W532" t="str">
-            <v/>
-          </cell>
-          <cell r="X532" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="533">
-          <cell r="V533" t="str">
-            <v/>
-          </cell>
-          <cell r="W533" t="str">
-            <v/>
-          </cell>
-          <cell r="X533" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="534">
-          <cell r="V534" t="str">
-            <v/>
-          </cell>
-          <cell r="W534" t="str">
-            <v/>
-          </cell>
-          <cell r="X534" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="535">
-          <cell r="V535" t="str">
-            <v/>
-          </cell>
-          <cell r="W535" t="str">
-            <v/>
-          </cell>
-          <cell r="X535" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="536">
-          <cell r="V536" t="str">
-            <v/>
-          </cell>
-          <cell r="W536" t="str">
-            <v/>
-          </cell>
-          <cell r="X536" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="537">
-          <cell r="V537" t="str">
-            <v/>
-          </cell>
-          <cell r="W537" t="str">
-            <v/>
-          </cell>
-          <cell r="X537" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="538">
-          <cell r="V538" t="str">
-            <v/>
-          </cell>
-          <cell r="W538" t="str">
-            <v/>
-          </cell>
-          <cell r="X538" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="539">
-          <cell r="V539" t="str">
-            <v/>
-          </cell>
-          <cell r="W539" t="str">
-            <v/>
-          </cell>
-          <cell r="X539" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="540">
-          <cell r="V540" t="str">
-            <v/>
-          </cell>
-          <cell r="W540" t="str">
-            <v/>
-          </cell>
-          <cell r="X540" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="541">
-          <cell r="V541" t="str">
-            <v/>
-          </cell>
-          <cell r="W541" t="str">
-            <v/>
-          </cell>
-          <cell r="X541" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="542">
-          <cell r="V542" t="str">
-            <v/>
-          </cell>
-          <cell r="W542" t="str">
-            <v/>
-          </cell>
-          <cell r="X542" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="543">
-          <cell r="V543" t="str">
-            <v/>
-          </cell>
-          <cell r="W543" t="str">
-            <v/>
-          </cell>
-          <cell r="X543" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="544">
-          <cell r="V544" t="str">
-            <v/>
-          </cell>
-          <cell r="W544" t="str">
-            <v/>
-          </cell>
-          <cell r="X544" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="545">
-          <cell r="V545" t="str">
-            <v/>
-          </cell>
-          <cell r="W545" t="str">
-            <v/>
-          </cell>
-          <cell r="X545" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="546">
-          <cell r="V546" t="str">
-            <v/>
-          </cell>
-          <cell r="W546" t="str">
-            <v/>
-          </cell>
-          <cell r="X546" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="547">
-          <cell r="V547" t="str">
-            <v/>
-          </cell>
-          <cell r="W547" t="str">
-            <v/>
-          </cell>
-          <cell r="X547" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="548">
-          <cell r="V548" t="str">
-            <v/>
-          </cell>
-          <cell r="W548" t="str">
-            <v/>
-          </cell>
-          <cell r="X548" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="549">
-          <cell r="V549" t="str">
-            <v/>
-          </cell>
-          <cell r="W549" t="str">
-            <v/>
-          </cell>
-          <cell r="X549" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="550">
-          <cell r="V550" t="str">
-            <v/>
-          </cell>
-          <cell r="W550" t="str">
-            <v/>
-          </cell>
-          <cell r="X550" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="551">
-          <cell r="V551" t="str">
-            <v/>
-          </cell>
-          <cell r="W551" t="str">
-            <v/>
-          </cell>
-          <cell r="X551" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="552">
-          <cell r="V552" t="str">
-            <v/>
-          </cell>
-          <cell r="W552" t="str">
-            <v/>
-          </cell>
-          <cell r="X552" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="553">
-          <cell r="V553" t="str">
-            <v/>
-          </cell>
-          <cell r="W553" t="str">
-            <v/>
-          </cell>
-          <cell r="X553" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="554">
-          <cell r="V554" t="str">
-            <v/>
-          </cell>
-          <cell r="W554" t="str">
-            <v/>
-          </cell>
-          <cell r="X554" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="555">
-          <cell r="V555" t="str">
-            <v/>
-          </cell>
-          <cell r="W555" t="str">
-            <v/>
-          </cell>
-          <cell r="X555" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="556">
-          <cell r="V556" t="str">
-            <v/>
-          </cell>
-          <cell r="W556" t="str">
-            <v/>
-          </cell>
-          <cell r="X556" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="557">
-          <cell r="V557" t="str">
-            <v/>
-          </cell>
-          <cell r="W557" t="str">
-            <v/>
-          </cell>
-          <cell r="X557" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="558">
-          <cell r="V558" t="str">
-            <v/>
-          </cell>
-          <cell r="W558" t="str">
-            <v/>
-          </cell>
-          <cell r="X558" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="559">
-          <cell r="V559" t="str">
-            <v/>
-          </cell>
-          <cell r="W559" t="str">
-            <v/>
-          </cell>
-          <cell r="X559" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="560">
-          <cell r="V560" t="str">
-            <v/>
-          </cell>
-          <cell r="W560" t="str">
-            <v/>
-          </cell>
-          <cell r="X560" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="561">
-          <cell r="V561" t="str">
-            <v/>
-          </cell>
-          <cell r="W561" t="str">
-            <v/>
-          </cell>
-          <cell r="X561" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="562">
-          <cell r="V562" t="str">
-            <v/>
-          </cell>
-          <cell r="W562" t="str">
-            <v/>
-          </cell>
-          <cell r="X562" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="563">
-          <cell r="V563" t="str">
-            <v/>
-          </cell>
-          <cell r="W563" t="str">
-            <v/>
-          </cell>
-          <cell r="X563" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="564">
-          <cell r="V564" t="str">
-            <v/>
-          </cell>
-          <cell r="W564" t="str">
-            <v/>
-          </cell>
-          <cell r="X564" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="565">
-          <cell r="V565" t="str">
-            <v/>
-          </cell>
-          <cell r="W565" t="str">
-            <v/>
-          </cell>
-          <cell r="X565" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="566">
-          <cell r="V566" t="str">
-            <v/>
-          </cell>
-          <cell r="W566" t="str">
-            <v/>
-          </cell>
-          <cell r="X566" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="567">
-          <cell r="V567" t="str">
-            <v/>
-          </cell>
-          <cell r="W567" t="str">
-            <v/>
-          </cell>
-          <cell r="X567" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="568">
-          <cell r="V568" t="str">
-            <v/>
-          </cell>
-          <cell r="W568" t="str">
-            <v/>
-          </cell>
-          <cell r="X568" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="569">
-          <cell r="V569" t="str">
-            <v/>
-          </cell>
-          <cell r="W569" t="str">
-            <v/>
-          </cell>
-          <cell r="X569" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="570">
-          <cell r="V570" t="str">
-            <v/>
-          </cell>
-          <cell r="W570" t="str">
-            <v/>
-          </cell>
-          <cell r="X570" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="571">
-          <cell r="V571" t="str">
-            <v/>
-          </cell>
-          <cell r="W571" t="str">
-            <v/>
-          </cell>
-          <cell r="X571" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="572">
-          <cell r="V572" t="str">
-            <v/>
-          </cell>
-          <cell r="W572" t="str">
-            <v/>
-          </cell>
-          <cell r="X572" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="573">
-          <cell r="V573" t="str">
-            <v/>
-          </cell>
-          <cell r="W573" t="str">
-            <v/>
-          </cell>
-          <cell r="X573" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="574">
-          <cell r="V574" t="str">
-            <v/>
-          </cell>
-          <cell r="W574" t="str">
-            <v/>
-          </cell>
-          <cell r="X574" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="575">
-          <cell r="V575" t="str">
-            <v/>
-          </cell>
-          <cell r="W575" t="str">
-            <v/>
-          </cell>
-          <cell r="X575" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="576">
-          <cell r="V576" t="str">
-            <v/>
-          </cell>
-          <cell r="W576" t="str">
-            <v/>
-          </cell>
-          <cell r="X576" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="577">
-          <cell r="V577" t="str">
-            <v/>
-          </cell>
-          <cell r="W577" t="str">
-            <v/>
-          </cell>
-          <cell r="X577" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="578">
-          <cell r="V578" t="str">
-            <v/>
-          </cell>
-          <cell r="W578" t="str">
-            <v/>
-          </cell>
-          <cell r="X578" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="579">
-          <cell r="V579" t="str">
-            <v/>
-          </cell>
-          <cell r="W579" t="str">
-            <v/>
-          </cell>
-          <cell r="X579" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="580">
-          <cell r="V580" t="str">
-            <v/>
-          </cell>
-          <cell r="W580" t="str">
-            <v/>
-          </cell>
-          <cell r="X580" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="581">
-          <cell r="V581" t="str">
-            <v/>
-          </cell>
-          <cell r="W581" t="str">
-            <v/>
-          </cell>
-          <cell r="X581" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="582">
-          <cell r="V582" t="str">
-            <v/>
-          </cell>
-          <cell r="W582" t="str">
-            <v/>
-          </cell>
-          <cell r="X582" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="583">
-          <cell r="V583" t="str">
-            <v/>
-          </cell>
-          <cell r="W583" t="str">
-            <v/>
-          </cell>
-          <cell r="X583" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="584">
-          <cell r="V584" t="str">
-            <v/>
-          </cell>
-          <cell r="W584" t="str">
-            <v/>
-          </cell>
-          <cell r="X584" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="585">
-          <cell r="V585" t="str">
-            <v/>
-          </cell>
-          <cell r="W585" t="str">
-            <v/>
-          </cell>
-          <cell r="X585" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="586">
-          <cell r="V586" t="str">
-            <v/>
-          </cell>
-          <cell r="W586" t="str">
-            <v/>
-          </cell>
-          <cell r="X586" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="587">
-          <cell r="V587" t="str">
-            <v/>
-          </cell>
-          <cell r="W587" t="str">
-            <v/>
-          </cell>
-          <cell r="X587" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="588">
-          <cell r="V588" t="str">
-            <v/>
-          </cell>
-          <cell r="W588" t="str">
-            <v/>
-          </cell>
-          <cell r="X588" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="589">
-          <cell r="V589" t="str">
-            <v/>
-          </cell>
-          <cell r="W589" t="str">
-            <v/>
-          </cell>
-          <cell r="X589" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="590">
-          <cell r="V590" t="str">
-            <v/>
-          </cell>
-          <cell r="W590" t="str">
-            <v/>
-          </cell>
-          <cell r="X590" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="591">
-          <cell r="V591" t="str">
-            <v/>
-          </cell>
-          <cell r="W591" t="str">
-            <v/>
-          </cell>
-          <cell r="X591" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="592">
-          <cell r="V592" t="str">
-            <v/>
-          </cell>
-          <cell r="W592" t="str">
-            <v/>
-          </cell>
-          <cell r="X592" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="593">
-          <cell r="V593" t="str">
-            <v/>
-          </cell>
-          <cell r="W593" t="str">
-            <v/>
-          </cell>
-          <cell r="X593" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="594">
-          <cell r="V594" t="str">
-            <v/>
-          </cell>
-          <cell r="W594" t="str">
-            <v/>
-          </cell>
-          <cell r="X594" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="595">
-          <cell r="V595" t="str">
-            <v/>
-          </cell>
-          <cell r="W595" t="str">
-            <v/>
-          </cell>
-          <cell r="X595" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="596">
-          <cell r="V596" t="str">
-            <v/>
-          </cell>
-          <cell r="W596" t="str">
-            <v/>
-          </cell>
-          <cell r="X596" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="597">
-          <cell r="V597" t="str">
-            <v/>
-          </cell>
-          <cell r="W597" t="str">
-            <v/>
-          </cell>
-          <cell r="X597" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="598">
-          <cell r="V598" t="str">
-            <v/>
-          </cell>
-          <cell r="W598" t="str">
-            <v/>
-          </cell>
-          <cell r="X598" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="599">
-          <cell r="V599" t="str">
-            <v/>
-          </cell>
-          <cell r="W599" t="str">
-            <v/>
-          </cell>
-          <cell r="X599" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="600">
-          <cell r="V600" t="str">
-            <v/>
-          </cell>
-          <cell r="W600" t="str">
-            <v/>
-          </cell>
-          <cell r="X600" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="601">
-          <cell r="V601" t="str">
-            <v/>
-          </cell>
-          <cell r="W601" t="str">
-            <v/>
-          </cell>
-          <cell r="X601" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="602">
-          <cell r="V602" t="str">
-            <v/>
-          </cell>
-          <cell r="W602" t="str">
-            <v/>
-          </cell>
-          <cell r="X602" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="603">
-          <cell r="V603" t="str">
-            <v/>
-          </cell>
-          <cell r="W603" t="str">
-            <v/>
-          </cell>
-          <cell r="X603" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="604">
-          <cell r="V604" t="str">
-            <v/>
-          </cell>
-          <cell r="W604" t="str">
-            <v/>
-          </cell>
-          <cell r="X604" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="605">
-          <cell r="V605" t="str">
-            <v/>
-          </cell>
-          <cell r="W605" t="str">
-            <v/>
-          </cell>
-          <cell r="X605" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="606">
-          <cell r="V606" t="str">
-            <v/>
-          </cell>
-          <cell r="W606" t="str">
-            <v/>
-          </cell>
-          <cell r="X606" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="607">
-          <cell r="V607" t="str">
-            <v/>
-          </cell>
-          <cell r="W607" t="str">
-            <v/>
-          </cell>
-          <cell r="X607" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="608">
-          <cell r="V608" t="str">
-            <v/>
-          </cell>
-          <cell r="W608" t="str">
-            <v/>
-          </cell>
-          <cell r="X608" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="609">
-          <cell r="V609" t="str">
-            <v/>
-          </cell>
-          <cell r="W609" t="str">
-            <v/>
-          </cell>
-          <cell r="X609" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="610">
-          <cell r="V610" t="str">
-            <v/>
-          </cell>
-          <cell r="W610" t="str">
-            <v/>
-          </cell>
-          <cell r="X610" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="611">
-          <cell r="V611" t="str">
-            <v/>
-          </cell>
-          <cell r="W611" t="str">
-            <v/>
-          </cell>
-          <cell r="X611" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="612">
-          <cell r="V612" t="str">
-            <v/>
-          </cell>
-          <cell r="W612" t="str">
-            <v/>
-          </cell>
-          <cell r="X612" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="613">
-          <cell r="V613" t="str">
-            <v/>
-          </cell>
-          <cell r="W613" t="str">
-            <v/>
-          </cell>
-          <cell r="X613" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="614">
-          <cell r="V614" t="str">
-            <v/>
-          </cell>
-          <cell r="W614" t="str">
-            <v/>
-          </cell>
-          <cell r="X614" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="615">
-          <cell r="V615" t="str">
-            <v/>
-          </cell>
-          <cell r="W615" t="str">
-            <v/>
-          </cell>
-          <cell r="X615" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="616">
-          <cell r="V616" t="str">
-            <v/>
-          </cell>
-          <cell r="W616" t="str">
-            <v/>
-          </cell>
-          <cell r="X616" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="617">
-          <cell r="V617" t="str">
-            <v/>
-          </cell>
-          <cell r="W617" t="str">
-            <v/>
-          </cell>
-          <cell r="X617" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="618">
-          <cell r="V618" t="str">
-            <v/>
-          </cell>
-          <cell r="W618" t="str">
-            <v/>
-          </cell>
-          <cell r="X618" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="619">
-          <cell r="V619" t="str">
-            <v/>
-          </cell>
-          <cell r="W619" t="str">
-            <v/>
-          </cell>
-          <cell r="X619" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="620">
-          <cell r="V620" t="str">
-            <v/>
-          </cell>
-          <cell r="W620" t="str">
-            <v/>
-          </cell>
-          <cell r="X620" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="621">
-          <cell r="V621" t="str">
-            <v/>
-          </cell>
-          <cell r="W621" t="str">
-            <v/>
-          </cell>
-          <cell r="X621" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="622">
-          <cell r="V622" t="str">
-            <v/>
-          </cell>
-          <cell r="W622" t="str">
-            <v/>
-          </cell>
-          <cell r="X622" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="623">
-          <cell r="V623" t="str">
-            <v/>
-          </cell>
-          <cell r="W623" t="str">
-            <v/>
-          </cell>
-          <cell r="X623" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="624">
-          <cell r="V624" t="str">
-            <v/>
-          </cell>
-          <cell r="W624" t="str">
-            <v/>
-          </cell>
-          <cell r="X624" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="625">
-          <cell r="V625" t="str">
-            <v/>
-          </cell>
-          <cell r="W625" t="str">
-            <v/>
-          </cell>
-          <cell r="X625" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="626">
-          <cell r="V626" t="str">
-            <v/>
-          </cell>
-          <cell r="W626" t="str">
-            <v/>
-          </cell>
-          <cell r="X626" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="627">
-          <cell r="V627" t="str">
-            <v/>
-          </cell>
-          <cell r="W627" t="str">
-            <v/>
-          </cell>
-          <cell r="X627" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="628">
-          <cell r="V628" t="str">
-            <v/>
-          </cell>
-          <cell r="W628" t="str">
-            <v/>
-          </cell>
-          <cell r="X628" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="629">
-          <cell r="V629" t="str">
-            <v/>
-          </cell>
-          <cell r="W629" t="str">
-            <v/>
-          </cell>
-          <cell r="X629" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="630">
-          <cell r="V630" t="str">
-            <v/>
-          </cell>
-          <cell r="W630" t="str">
-            <v/>
-          </cell>
-          <cell r="X630" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="631">
-          <cell r="V631" t="str">
-            <v/>
-          </cell>
-          <cell r="W631" t="str">
-            <v/>
-          </cell>
-          <cell r="X631" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="632">
-          <cell r="V632" t="str">
-            <v/>
-          </cell>
-          <cell r="W632" t="str">
-            <v/>
-          </cell>
-          <cell r="X632" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="633">
-          <cell r="V633" t="str">
-            <v/>
-          </cell>
-          <cell r="W633" t="str">
-            <v/>
-          </cell>
-          <cell r="X633" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="634">
-          <cell r="V634" t="str">
-            <v/>
-          </cell>
-          <cell r="W634" t="str">
-            <v/>
-          </cell>
-          <cell r="X634" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="635">
-          <cell r="V635" t="str">
-            <v/>
-          </cell>
-          <cell r="W635" t="str">
-            <v/>
-          </cell>
-          <cell r="X635" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="636">
-          <cell r="V636" t="str">
-            <v/>
-          </cell>
-          <cell r="W636" t="str">
-            <v/>
-          </cell>
-          <cell r="X636" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="637">
-          <cell r="V637" t="str">
-            <v/>
-          </cell>
-          <cell r="W637" t="str">
-            <v/>
-          </cell>
-          <cell r="X637" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="638">
-          <cell r="V638" t="str">
-            <v/>
-          </cell>
-          <cell r="W638" t="str">
-            <v/>
-          </cell>
-          <cell r="X638" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="639">
-          <cell r="V639" t="str">
-            <v/>
-          </cell>
-          <cell r="W639" t="str">
-            <v/>
-          </cell>
-          <cell r="X639" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="640">
-          <cell r="V640" t="str">
-            <v/>
-          </cell>
-          <cell r="W640" t="str">
-            <v/>
-          </cell>
-          <cell r="X640" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="641">
-          <cell r="V641" t="str">
-            <v/>
-          </cell>
-          <cell r="W641" t="str">
-            <v/>
-          </cell>
-          <cell r="X641" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="642">
-          <cell r="V642" t="str">
-            <v/>
-          </cell>
-          <cell r="W642" t="str">
-            <v/>
-          </cell>
-          <cell r="X642" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="643">
-          <cell r="V643" t="str">
-            <v/>
-          </cell>
-          <cell r="W643" t="str">
-            <v/>
-          </cell>
-          <cell r="X643" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="644">
-          <cell r="V644" t="str">
-            <v/>
-          </cell>
-          <cell r="W644" t="str">
-            <v/>
-          </cell>
-          <cell r="X644" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="645">
-          <cell r="V645" t="str">
-            <v/>
-          </cell>
-          <cell r="W645" t="str">
-            <v/>
-          </cell>
-          <cell r="X645" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="646">
-          <cell r="V646" t="str">
-            <v/>
-          </cell>
-          <cell r="W646" t="str">
-            <v/>
-          </cell>
-          <cell r="X646" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="647">
-          <cell r="V647" t="str">
-            <v/>
-          </cell>
-          <cell r="W647" t="str">
-            <v/>
-          </cell>
-          <cell r="X647" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="648">
-          <cell r="V648" t="str">
-            <v/>
-          </cell>
-          <cell r="W648" t="str">
-            <v/>
-          </cell>
-          <cell r="X648" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="649">
-          <cell r="V649" t="str">
-            <v/>
-          </cell>
-          <cell r="W649" t="str">
-            <v/>
-          </cell>
-          <cell r="X649" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="650">
-          <cell r="V650" t="str">
-            <v/>
-          </cell>
-          <cell r="W650" t="str">
-            <v/>
-          </cell>
-          <cell r="X650" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="651">
-          <cell r="V651" t="str">
-            <v/>
-          </cell>
-          <cell r="W651" t="str">
-            <v/>
-          </cell>
-          <cell r="X651" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="652">
-          <cell r="V652" t="str">
-            <v/>
-          </cell>
-          <cell r="W652" t="str">
-            <v/>
-          </cell>
-          <cell r="X652" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="653">
-          <cell r="V653" t="str">
-            <v/>
-          </cell>
-          <cell r="W653" t="str">
-            <v/>
-          </cell>
-          <cell r="X653" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="654">
-          <cell r="V654" t="str">
-            <v/>
-          </cell>
-          <cell r="W654" t="str">
-            <v/>
-          </cell>
-          <cell r="X654" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="655">
-          <cell r="V655" t="str">
-            <v/>
-          </cell>
-          <cell r="W655" t="str">
-            <v/>
-          </cell>
-          <cell r="X655" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="656">
-          <cell r="V656" t="str">
-            <v/>
-          </cell>
-          <cell r="W656" t="str">
-            <v/>
-          </cell>
-          <cell r="X656" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="657">
-          <cell r="V657" t="str">
-            <v/>
-          </cell>
-          <cell r="W657" t="str">
-            <v/>
-          </cell>
-          <cell r="X657" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="658">
-          <cell r="V658" t="str">
-            <v/>
-          </cell>
-          <cell r="W658" t="str">
-            <v/>
-          </cell>
-          <cell r="X658" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="659">
-          <cell r="V659" t="str">
-            <v/>
-          </cell>
-          <cell r="W659" t="str">
-            <v/>
-          </cell>
-          <cell r="X659" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="660">
-          <cell r="V660" t="str">
-            <v/>
-          </cell>
-          <cell r="W660" t="str">
-            <v/>
-          </cell>
-          <cell r="X660" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="661">
-          <cell r="V661" t="str">
-            <v/>
-          </cell>
-          <cell r="W661" t="str">
-            <v/>
-          </cell>
-          <cell r="X661" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="662">
-          <cell r="V662" t="str">
-            <v/>
-          </cell>
-          <cell r="W662" t="str">
-            <v/>
-          </cell>
-          <cell r="X662" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="663">
-          <cell r="V663" t="str">
-            <v/>
-          </cell>
-          <cell r="W663" t="str">
-            <v/>
-          </cell>
-          <cell r="X663" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="664">
-          <cell r="V664" t="str">
-            <v/>
-          </cell>
-          <cell r="W664" t="str">
-            <v/>
-          </cell>
-          <cell r="X664" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="665">
-          <cell r="V665" t="str">
-            <v/>
-          </cell>
-          <cell r="W665" t="str">
-            <v/>
-          </cell>
-          <cell r="X665" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="666">
-          <cell r="V666" t="str">
-            <v/>
-          </cell>
-          <cell r="W666" t="str">
-            <v/>
-          </cell>
-          <cell r="X666" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="667">
-          <cell r="V667" t="str">
-            <v/>
-          </cell>
-          <cell r="W667" t="str">
-            <v/>
-          </cell>
-          <cell r="X667" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="668">
-          <cell r="V668" t="str">
-            <v/>
-          </cell>
-          <cell r="W668" t="str">
-            <v/>
-          </cell>
-          <cell r="X668" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="669">
-          <cell r="V669" t="str">
-            <v/>
-          </cell>
-          <cell r="W669" t="str">
-            <v/>
-          </cell>
-          <cell r="X669" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="670">
-          <cell r="V670" t="str">
-            <v/>
-          </cell>
-          <cell r="W670" t="str">
-            <v/>
-          </cell>
-          <cell r="X670" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="671">
-          <cell r="V671" t="str">
-            <v/>
-          </cell>
-          <cell r="W671" t="str">
-            <v/>
-          </cell>
-          <cell r="X671" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="672">
-          <cell r="V672" t="str">
-            <v/>
-          </cell>
-          <cell r="W672" t="str">
-            <v/>
-          </cell>
-          <cell r="X672" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="673">
-          <cell r="V673" t="str">
-            <v/>
-          </cell>
-          <cell r="W673" t="str">
-            <v/>
-          </cell>
-          <cell r="X673" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="674">
-          <cell r="V674" t="str">
-            <v/>
-          </cell>
-          <cell r="W674" t="str">
-            <v/>
-          </cell>
-          <cell r="X674" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="675">
-          <cell r="V675" t="str">
-            <v/>
-          </cell>
-          <cell r="W675" t="str">
-            <v/>
-          </cell>
-          <cell r="X675" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="676">
-          <cell r="V676" t="str">
-            <v/>
-          </cell>
-          <cell r="W676" t="str">
-            <v/>
-          </cell>
-          <cell r="X676" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="677">
-          <cell r="V677" t="str">
-            <v/>
-          </cell>
-          <cell r="W677" t="str">
-            <v/>
-          </cell>
-          <cell r="X677" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="678">
-          <cell r="V678" t="str">
-            <v/>
-          </cell>
-          <cell r="W678" t="str">
-            <v/>
-          </cell>
-          <cell r="X678" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="679">
-          <cell r="V679" t="str">
-            <v/>
-          </cell>
-          <cell r="W679" t="str">
-            <v/>
-          </cell>
-          <cell r="X679" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="680">
-          <cell r="V680" t="str">
-            <v/>
-          </cell>
-          <cell r="W680" t="str">
-            <v/>
-          </cell>
-          <cell r="X680" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="681">
-          <cell r="V681" t="str">
-            <v/>
-          </cell>
-          <cell r="W681" t="str">
-            <v/>
-          </cell>
-          <cell r="X681" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="682">
-          <cell r="V682" t="str">
-            <v/>
-          </cell>
-          <cell r="W682" t="str">
-            <v/>
-          </cell>
-          <cell r="X682" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="683">
-          <cell r="V683" t="str">
-            <v/>
-          </cell>
-          <cell r="W683" t="str">
-            <v/>
-          </cell>
-          <cell r="X683" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-        <row r="684">
-          <cell r="V684" t="str">
-            <v/>
-          </cell>
-          <cell r="W684" t="str">
-            <v/>
-          </cell>
-          <cell r="X684" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </v>
-          </cell>
-        </row>
-        <row r="685">
-          <cell r="V685" t="str">
-            <v/>
-          </cell>
-          <cell r="W685" t="str">
-            <v/>
-          </cell>
-          <cell r="X685" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </v>
-          </cell>
-        </row>
-        <row r="686">
-          <cell r="V686" t="str">
-            <v/>
-          </cell>
-          <cell r="W686" t="str">
-            <v/>
-          </cell>
-          <cell r="X686" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </v>
-          </cell>
-        </row>
-        <row r="687">
-          <cell r="V687" t="str">
-            <v/>
-          </cell>
-          <cell r="W687" t="str">
-            <v/>
-          </cell>
-          <cell r="X687" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </v>
-          </cell>
-        </row>
-        <row r="688">
-          <cell r="V688" t="str">
-            <v/>
-          </cell>
-          <cell r="W688" t="str">
-            <v/>
-          </cell>
-          <cell r="X688" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </v>
-          </cell>
-        </row>
-        <row r="689">
-          <cell r="V689" t="str">
-            <v/>
-          </cell>
-          <cell r="W689" t="str">
-            <v/>
-          </cell>
-          <cell r="X689" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </v>
-          </cell>
-        </row>
-        <row r="690">
-          <cell r="V690" t="str">
-            <v/>
-          </cell>
-          <cell r="W690" t="str">
-            <v/>
-          </cell>
-          <cell r="X690" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </v>
-          </cell>
-        </row>
-        <row r="691">
-          <cell r="V691" t="str">
-            <v/>
-          </cell>
-          <cell r="W691" t="str">
-            <v/>
-          </cell>
-          <cell r="X691" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </v>
-          </cell>
-        </row>
-        <row r="692">
-          <cell r="V692" t="str">
-            <v/>
-          </cell>
-          <cell r="W692" t="str">
-            <v/>
-          </cell>
-          <cell r="X692" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </v>
-          </cell>
-        </row>
-        <row r="693">
-          <cell r="V693" t="str">
-            <v/>
-          </cell>
-          <cell r="W693" t="str">
-            <v/>
-          </cell>
-          <cell r="X693" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </v>
-          </cell>
-        </row>
-        <row r="694">
-          <cell r="V694" t="str">
-            <v/>
-          </cell>
-          <cell r="W694" t="str">
-            <v/>
-          </cell>
-          <cell r="X694" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </v>
-          </cell>
-        </row>
-        <row r="695">
-          <cell r="V695" t="str">
-            <v/>
-          </cell>
-          <cell r="W695" t="str">
-            <v/>
-          </cell>
-          <cell r="X695" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </v>
-          </cell>
-        </row>
-        <row r="696">
-          <cell r="V696" t="str">
-            <v/>
-          </cell>
-          <cell r="W696" t="str">
-            <v/>
-          </cell>
-          <cell r="X696" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </v>
-          </cell>
-        </row>
-        <row r="697">
-          <cell r="V697" t="str">
-            <v/>
-          </cell>
-          <cell r="W697" t="str">
-            <v/>
-          </cell>
-          <cell r="X697" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </v>
-          </cell>
-        </row>
-        <row r="698">
-          <cell r="V698" t="str">
-            <v/>
-          </cell>
-          <cell r="W698" t="str">
-            <v/>
-          </cell>
-          <cell r="X698" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </v>
-          </cell>
-        </row>
-        <row r="699">
-          <cell r="V699" t="str">
-            <v/>
-          </cell>
-          <cell r="W699" t="str">
-            <v/>
-          </cell>
-          <cell r="X699" t="str">
-            <v xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
@@ -9582,9 +1838,6 @@
       <sheetName val="Limesurvey"/>
     </sheetNames>
     <definedNames>
-      <definedName name="SF40_KlickenSieAuf"/>
-      <definedName name="SF40_SelectedKlickenSieAuf"/>
-      <definedName name="TemplateFill"/>
       <definedName name="V_TemplateFill" refersTo="='Vorgaben Questions'!$A$4:$A$32"/>
     </definedNames>
     <sheetDataSet>
@@ -9899,8 +2152,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AMJ45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
@@ -10121,18 +2374,16 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="10" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F23" s="13"/>
+      <c r="A23" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="10" t="e">
         <f>#N/A</f>
@@ -10141,112 +2392,122 @@
       <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="10" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
       <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B27" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B31" s="10" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="7" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B33" s="7" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="14">
-        <v>100</v>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="7" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B37" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="10" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B39" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C39" s="1">
         <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>45</v>
       </c>
     </row>
@@ -10273,6 +2534,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10455,8 +2717,8 @@
     </row>
     <row r="2" spans="1:56" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:56" s="18" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="E3" s="18">
         <v>1</v>
       </c>
@@ -10610,8 +2872,8 @@
       <c r="BD3" s="19"/>
     </row>
     <row r="4" spans="1:56" s="18" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
       <c r="E4" s="18" t="s">
         <v>15</v>
       </c>
@@ -14411,7 +6673,7 @@
       <c r="F1" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="32" t="s">
         <v>241</v>
       </c>
       <c r="H1" s="28" t="s">
@@ -41202,28 +33464,28 @@
       <c r="AO678" s="26"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A4 A19:A1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A18">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A18 A5:A12">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>LEFT(N5,1)="A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>$T5</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -41235,7 +33497,7 @@
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
             <control shapeId="2051" r:id="rId3" name="Drop Down 3">
-              <controlPr defaultSize="0" autoLine="0" autoPict="0" macro="[4]!TemplateFill">
+              <controlPr defaultSize="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
